--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$21</definedName>
   </definedNames>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -706,22 +706,22 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>actionyardcare.com</t>
+          <t>anyandallservices.com</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Action Lawn &amp; Yardcare</t>
+          <t>Any &amp; All Services</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
+          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -746,28 +746,28 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>How high should you mow a Utah lawn?</t>
+          <t>6 signs you need an electrician, according to NFPA</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -777,22 +777,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>danielswildlife.com</t>
+          <t>sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Daniel's Wildlife &amp; Pest Control</t>
+          <t>Sterling Tree Co.</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
+          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -815,30 +815,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>Found mouse droppings? How to clean up safely</t>
+          <t>Why topping hurts trees (and what arborists do instead)</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -848,22 +844,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>greenjanitorialservice.com</t>
+          <t>actionyardcare.com</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Green Janitorial Services</t>
+          <t>Action Lawn &amp; Yardcare</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
+          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -886,15 +882,19 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Is that cleaner really green? How to read eco labels</t>
+          <t>How high should you mow a Utah lawn?</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -905,7 +905,7 @@
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
         </is>
       </c>
     </row>
@@ -915,22 +915,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>emetplumbingservices.com</t>
+          <t>danielswildlife.com</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Emet Plumbing Heating &amp; Air</t>
+          <t>Daniel's Wildlife &amp; Pest Control</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
+          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Furnace filters and MERV ratings, explained</t>
+          <t>Found mouse droppings? How to clean up safely</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -976,7 +976,7 @@
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
         </is>
       </c>
     </row>
@@ -986,22 +986,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>everworklandscape.com</t>
+          <t>greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Everwork Property Maintenance &amp; Landscaping</t>
+          <t>Green Janitorial Services</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
+          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1024,19 +1024,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>How to water a Utah lawn: deeper, less often</t>
+          <t>Is that cleaner really green? How to read eco labels</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1047,7 +1043,7 @@
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1053,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>iraut.com</t>
+          <t>emetplumbingservices.com</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Investment Realty Advisors</t>
+          <t>Emet Plumbing Heating &amp; Air</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
+          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1097,17 +1093,17 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>1031 exchange rules: what Utah real estate investors need to know</t>
+          <t>Furnace filters and MERV ratings, explained</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1118,7 +1114,7 @@
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
         </is>
       </c>
     </row>
@@ -1128,22 +1124,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>applianceserviceut.com</t>
+          <t>everworklandscape.com</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ASI Appliance Services</t>
+          <t>Everwork Property Maintenance &amp; Landscaping</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
+          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1168,17 +1164,17 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Clothes dryer fire safety: the lint habit that matters most</t>
+          <t>How to water a Utah lawn: deeper, less often</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -1189,7 +1185,7 @@
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
         </is>
       </c>
     </row>
@@ -1199,22 +1195,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>triplejlandscaping.com</t>
+          <t>iraut.com</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Triple J Landscaping</t>
+          <t>Investment Realty Advisors</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
+          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1239,17 +1235,17 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>How much to water your lawn in Utah: the half-inch rule</t>
+          <t>1031 exchange rules: what Utah real estate investors need to know</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -1260,7 +1256,7 @@
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1266,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>joestreecareutah.com</t>
+          <t>applianceserviceut.com</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Joe's Tree Care / Joe's Stump Grinding</t>
+          <t>ASI Appliance Services</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
+          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1310,17 +1306,17 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>How to water trees in Utah: deep, slow and less often</t>
+          <t>Clothes dryer fire safety: the lint habit that matters most</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -1331,7 +1327,7 @@
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1337,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>utahbluechipcarpetcleaning.com</t>
+          <t>triplejlandscaping.com</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Blue Chip Carpet Cleaning</t>
+          <t>Triple J Landscaping</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
+          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1381,17 +1377,17 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
+          <t>How much to water your lawn in Utah: the half-inch rule</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1402,7 +1398,7 @@
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
         </is>
       </c>
     </row>
@@ -1412,22 +1408,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>trustyappliancerepairutah.com</t>
+          <t>joestreecareutah.com</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Trusty Appliance Repair</t>
+          <t>Joe's Tree Care / Joe's Stump Grinding</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
+          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1452,17 +1448,17 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
+          <t>How to water trees in Utah: deep, slow and less often</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -1473,7 +1469,7 @@
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
         </is>
       </c>
     </row>
@@ -1483,22 +1479,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>vogldirect.com</t>
+          <t>utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Vogl Direct</t>
+          <t>Blue Chip Carpet Cleaning</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Eagle Mountain</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
+          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1523,17 +1519,17 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
+          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1544,7 +1540,7 @@
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
         </is>
       </c>
     </row>
@@ -1554,22 +1550,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ahc-utah.com</t>
+          <t>trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Affordable Heating &amp; Cooling</t>
+          <t>Trusty Appliance Repair</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
+          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1594,17 +1590,17 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
+          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -1615,7 +1611,7 @@
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1621,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>mountainwindowcleaning.com</t>
+          <t>vogldirect.com</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Mountain Window Cleaning</t>
+          <t>Vogl Direct</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Eagle Mountain</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
+          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1650,7 +1646,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1665,28 +1661,28 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Why birds hit your windows, and how to stop it</t>
+          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1692,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>rwkconstruction.com</t>
+          <t>ahc-utah.com</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>RWK Construction Co.</t>
+          <t>Affordable Heating &amp; Cooling</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Bluffdale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
+          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1721,7 +1717,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1736,28 +1732,28 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
+          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -1767,22 +1763,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>5starkb.com</t>
+          <t>mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>5 Star Kitchen and Bath</t>
+          <t>Mountain Window Cleaning</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
+          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1807,17 +1803,17 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
+          <t>Why birds hit your windows, and how to stop it</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1828,7 +1824,7 @@
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1834,27 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>acs-hoa.com</t>
+          <t>rwkconstruction.com</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Advanced Community Services</t>
+          <t>RWK Construction Co.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Bluffdale</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
+          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -1873,22 +1869,22 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>The HOA board's winter checklist for Utah communities</t>
+          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -1899,7 +1895,7 @@
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -1909,27 +1905,27 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>equitypmusa.com</t>
+          <t>5starkb.com</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Equity Real Estate Property Management</t>
+          <t>5 Star Kitchen and Bath</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
+          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1944,22 +1940,22 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>How to spot a rental listing scam before you pay a dime</t>
+          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1970,7 +1966,7 @@
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
         </is>
       </c>
     </row>
@@ -1980,27 +1976,27 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>abode.cleaning</t>
+          <t>acs-hoa.com</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Abode House Cleaning</t>
+          <t>Advanced Community Services</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
+          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link)</t>
+          <t>Anyone with the link</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -2015,22 +2011,22 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (21 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cleaning products and the air in your home: a plain-language guide</t>
+          <t>The HOA board's winter checklist for Utah communities</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -2041,7 +2037,7 @@
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
         </is>
       </c>
     </row>
@@ -2051,22 +2047,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>lockthesmithut.com</t>
+          <t>equitypmusa.com</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Lockthesmith</t>
+          <t>Equity Real Estate Property Management</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
+          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2091,17 +2087,17 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Hot cars and locked doors: what every Utah driver should know</t>
+          <t>How to spot a rental listing scam before you pay a dime</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -2112,7 +2108,7 @@
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
         </is>
       </c>
     </row>
@@ -2122,22 +2118,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>rasmussenlandscapes.com</t>
+          <t>abode.cleaning</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Rasmussen Landscapes</t>
+          <t>Abode House Cleaning</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
+          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2162,17 +2158,17 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>When should you start watering your lawn in Utah?</t>
+          <t>Cleaning products and the air in your home: a plain-language guide</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2183,7 +2179,7 @@
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
         </is>
       </c>
     </row>
@@ -2193,27 +2189,27 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ezelectric.com</t>
+          <t>lockthesmithut.com</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>EZ Electric</t>
+          <t>Lockthesmith</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
+          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link)</t>
+          <t>Anyone with the link</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2228,22 +2224,22 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (21 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
+          <t>Hot cars and locked doors: what every Utah driver should know</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -2254,7 +2250,7 @@
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
         </is>
       </c>
     </row>
@@ -2264,22 +2260,22 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>therepairpros.com</t>
+          <t>rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>The Repair Pros</t>
+          <t>Rasmussen Landscapes</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
+          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2304,17 +2300,17 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Repair or replace? How long appliances actually last</t>
+          <t>When should you start watering your lawn in Utah?</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -2325,7 +2321,7 @@
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2331,27 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>pestx.org</t>
+          <t>ezelectric.com</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pestx</t>
+          <t>EZ Electric</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
+          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2370,22 +2366,22 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
+          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -2396,7 +2392,7 @@
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
         </is>
       </c>
     </row>
@@ -2406,32 +2402,32 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>foundationrepairogden.com</t>
+          <t>therepairpros.com</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Fortified Foundations</t>
+          <t>The Repair Pros</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
+          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -2441,37 +2437,33 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
+          <t>Repair or replace? How long appliances actually last</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2473,22 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>rhinofoundationsystems.com</t>
+          <t>pestx.org</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Rhino Foundation Systems</t>
+          <t>Pestx</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>American Fork</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
+          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2506,7 +2498,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -2516,37 +2508,33 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
+          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -2556,22 +2544,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>sandsroofingutah.com</t>
+          <t>foundationrepairogden.com</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>S&amp;S Roofing, Inc.</t>
+          <t>Fortified Foundations</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
+          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2591,22 +2579,22 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 20 Oct</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
+          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2616,12 +2604,12 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
+          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
+          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
         </is>
       </c>
     </row>
@@ -2631,22 +2619,22 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>stgeorgeconcreteleveling.com</t>
+          <t>rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>St. George Concrete Leveling</t>
+          <t>Rhino Foundation Systems</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>American Fork</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
+          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2666,22 +2654,22 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
+          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2691,12 +2679,12 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
+          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
+          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
         </is>
       </c>
     </row>
@@ -2706,22 +2694,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>m3industriesconcrete.com</t>
+          <t>sandsroofingutah.com</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>M3 Industries</t>
+          <t>S&amp;S Roofing, Inc.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
+          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2741,22 +2729,22 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Premium redesign (v2) published 20 Oct</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
+          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2766,12 +2754,12 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
+          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
+          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
         </is>
       </c>
     </row>
@@ -2781,22 +2769,22 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>thedisasterrepairteam.com</t>
+          <t>stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Disaster Repair Team</t>
+          <t>St. George Concrete Leveling</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
+          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2821,17 +2809,17 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
+          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2841,12 +2829,12 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
+          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
+          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
         </is>
       </c>
     </row>
@@ -2856,22 +2844,22 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>poly-lift.com</t>
+          <t>m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Poly-Lift</t>
+          <t>M3 Industries</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
+          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2896,17 +2884,17 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
+          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2916,12 +2904,12 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
+          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
+          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
         </is>
       </c>
     </row>
@@ -2931,22 +2919,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>stgeorgehomeservices.com</t>
+          <t>thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>St. George Home Services</t>
+          <t>Disaster Repair Team</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
+          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2971,17 +2959,17 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
+          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -2991,12 +2979,12 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
+          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
+          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
         </is>
       </c>
     </row>
@@ -3006,22 +2994,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>cleartopsolutions.shop</t>
+          <t>poly-lift.com</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>ClearTop Solutions</t>
+          <t>Poly-Lift</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
+          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -3046,17 +3034,17 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
+          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -3066,12 +3054,12 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
+          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
+          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
         </is>
       </c>
     </row>
@@ -3081,22 +3069,22 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>jsprofinish.com</t>
+          <t>stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>JS ProFinish</t>
+          <t>St. George Home Services</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Clearfield</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
+          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -3121,17 +3109,17 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
+          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -3141,12 +3129,12 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
+          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
+          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3144,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>armour-crete.com</t>
+          <t>cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Armour Crete</t>
+          <t>ClearTop Solutions</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3171,7 +3159,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
+          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3196,17 +3184,17 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
+          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -3216,12 +3204,12 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
+          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
+          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
         </is>
       </c>
     </row>
@@ -3231,22 +3219,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>swiftrestoreutah.com</t>
+          <t>jsprofinish.com</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Swift Restoration and Remodeling</t>
+          <t>JS ProFinish</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>Clearfield</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
+          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3269,15 +3257,19 @@
           <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -3287,12 +3279,12 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
+          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
+          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
         </is>
       </c>
     </row>
@@ -3302,22 +3294,22 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>exceptional-roofing.com</t>
+          <t>armour-crete.com</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Exceptional Roofing</t>
+          <t>Armour Crete</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
+          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -3327,7 +3319,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -3337,22 +3329,22 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
+          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -3362,12 +3354,12 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
+          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
+          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
         </is>
       </c>
     </row>
@@ -3377,22 +3369,22 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>sfrutah.com</t>
+          <t>swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Superior Foundation Repair Utah</t>
+          <t>Swift Restoration and Remodeling</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City &amp; St. George</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
+          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -3402,7 +3394,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -3412,22 +3404,18 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
+          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -3437,12 +3425,12 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
+          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
+          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
         </is>
       </c>
     </row>
@@ -3452,22 +3440,22 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>dryhouse.com</t>
+          <t>exceptional-roofing.com</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Rocky Mountain Waterproofing</t>
+          <t>Exceptional Roofing</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
+          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3490,15 +3478,19 @@
           <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
+          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -3508,12 +3500,12 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
+          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
+          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
         </is>
       </c>
     </row>
@@ -3523,22 +3515,22 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>davenportfoundationrepair.com</t>
+          <t>sfrutah.com</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Davenport Foundation Repair</t>
+          <t>Superior Foundation Repair Utah</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Salt Lake City &amp; St. George</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
+          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3563,17 +3555,17 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
+          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -3583,12 +3575,12 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
+          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
+          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
         </is>
       </c>
     </row>
@@ -3598,22 +3590,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>saltcityroofers.com</t>
+          <t>dryhouse.com</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Salt City Roofers</t>
+          <t>Rocky Mountain Waterproofing</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
+          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3623,7 +3615,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -3633,22 +3625,18 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>Built premium from the start (19 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
+          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -3658,12 +3646,12 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
+          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
+          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
         </is>
       </c>
     </row>
@@ -3673,22 +3661,22 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>utahroofingpros.com</t>
+          <t>davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Utah Roofing Pros</t>
+          <t>Davenport Foundation Repair</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
+          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3698,7 +3686,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3708,22 +3696,22 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>514</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
+          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3733,12 +3721,12 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
+          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>The current city pages use AI-generated photos; none are used</t>
+          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
         </is>
       </c>
     </row>
@@ -3748,22 +3736,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>xperienceroofing.com</t>
+          <t>saltcityroofers.com</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Xperience Roofing</t>
+          <t>Salt City Roofers</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
+          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3788,13 +3776,17 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
+        </is>
+      </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3804,12 +3796,12 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
+          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
+          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
         </is>
       </c>
     </row>
@@ -3819,22 +3811,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>utahoneroofing.com</t>
+          <t>utahroofingpros.com</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Utah One Roofing / One Roofing LLC</t>
+          <t>Utah Roofing Pros</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
+          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3859,17 +3851,17 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
+          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3879,12 +3871,12 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
+          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
+          <t>The current city pages use AI-generated photos; none are used</t>
         </is>
       </c>
     </row>
@@ -3894,22 +3886,22 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>roofrepairsaltlakecity.com</t>
+          <t>xperienceroofing.com</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Roof Repair Salt Lake City</t>
+          <t>Xperience Roofing</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
+          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3929,18 +3921,18 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3950,12 +3942,12 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
+          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
         </is>
       </c>
     </row>
@@ -3965,22 +3957,22 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>skybridgeroofings.com</t>
+          <t>utahoneroofing.com</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Sky Bridge Roofing</t>
+          <t>Utah One Roofing / One Roofing LLC</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
+          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -4000,22 +3992,22 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct)</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
+          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -4025,12 +4017,12 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4032,12 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>oakleyroofingslc.com</t>
+          <t>roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Oakley Roofing</t>
+          <t>Roof Repair Salt Lake City</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -4055,7 +4047,7 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
+          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -4065,7 +4057,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -4075,22 +4067,18 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (17 Oct)</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -4098,10 +4086,14 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+        </is>
+      </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
         </is>
       </c>
     </row>
@@ -4111,22 +4103,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>mandmgutters.com</t>
+          <t>skybridgeroofings.com</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>M&amp;M Gutters &amp; Exteriors</t>
+          <t>Sky Bridge Roofing</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
+          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -4136,7 +4128,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -4146,22 +4138,22 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Built premium from the start (18 Oct)</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
+          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4171,12 +4163,12 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
+          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4178,12 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>roofwiseut.com</t>
+          <t>oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>RoofWise</t>
+          <t>Oakley Roofing</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -4201,7 +4193,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
+          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -4221,22 +4213,22 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Built premium from the start (17 Oct)</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>What Does Hail Damage Look Like on a Roof?</t>
+          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -4244,14 +4236,10 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
-        </is>
-      </c>
+      <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
         </is>
       </c>
     </row>
@@ -4261,22 +4249,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>jordanriverroofing.com</t>
+          <t>mandmgutters.com</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Jordan River Roofing</t>
+          <t>M&amp;M Gutters &amp; Exteriors</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
+          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -4301,17 +4289,17 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
+          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4321,12 +4309,12 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4324,12 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>jemzaroofing.com</t>
+          <t>roofwiseut.com</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Jemza Roofing</t>
+          <t>RoofWise</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -4351,7 +4339,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
+          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -4371,22 +4359,22 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
+          <t>What Does Hail Damage Look Like on a Roof?</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4396,12 +4384,12 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
         </is>
       </c>
     </row>
@@ -4411,22 +4399,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>jandnroofing.com</t>
+          <t>jordanriverroofing.com</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>J &amp; N Roofing Maintenance, LLC</t>
+          <t>Jordan River Roofing</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
+          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -4446,22 +4434,22 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>How Far Should Shingles Overhang the Drip Edge?</t>
+          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -4471,12 +4459,12 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
         </is>
       </c>
     </row>
@@ -4486,22 +4474,22 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>gprroofing.com</t>
+          <t>jemzaroofing.com</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Go Pro Roofing</t>
+          <t>Jemza Roofing</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -4526,17 +4514,17 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>How Are Valleys Done on a Metal Roof?</t>
+          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -4546,10 +4534,14 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O54" s="7" t="inlineStr"/>
+          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -4557,22 +4549,22 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>pioneerroofingutah.com</t>
+          <t>jandnroofing.com</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Pioneer Roofing Co</t>
+          <t>J &amp; N Roofing Maintenance, LLC</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, est. 1980</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -4597,17 +4589,17 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
+          <t>How Far Should Shingles Overhang the Drip Edge?</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4617,10 +4609,14 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr"/>
+          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -4628,22 +4624,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>ezroofingnow.com</t>
+          <t>gprroofing.com</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>EZ Roofing</t>
+          <t>Go Pro Roofing</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -4668,17 +4664,17 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>The Best Time of Year to Replace a Roof in Utah</t>
+          <t>How Are Valleys Done on a Metal Roof?</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4688,7 +4684,7 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
+          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr"/>
@@ -4699,22 +4695,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>customroofs.biz</t>
+          <t>pioneerroofingutah.com</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Custom Roofing LLC</t>
+          <t>Pioneer Roofing Co</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City, est. 1980</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -4739,17 +4735,17 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Why Does Copper Turn Green?</t>
+          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4759,7 +4755,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
+          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr"/>
@@ -4770,22 +4766,22 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>aluminumlockroofing.com</t>
+          <t>ezroofingnow.com</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Aluminum Lock Roofing</t>
+          <t>EZ Roofing</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Salt Lake City, UT &amp; Cabot, AR</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4810,17 +4806,17 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>253</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>Can You Put a New Roof Over an Old Roof?</t>
+          <t>The Best Time of Year to Replace a Roof in Utah</t>
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -4830,7 +4826,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
+          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr"/>
@@ -4841,22 +4837,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>aestheticroofing.com</t>
+          <t>customroofs.biz</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Aesthetic Roofing</t>
+          <t>Custom Roofing LLC</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -4866,7 +4862,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -4881,17 +4877,17 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>What Causes Roof Leaks?</t>
+          <t>Why Does Copper Turn Green?</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -4901,7 +4897,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
+          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr"/>
@@ -4912,18 +4908,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>amcoroof.com</t>
+          <t>aluminumlockroofing.com</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>American Roofing Company</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr"/>
+          <t>Aluminum Lock Roofing</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>How to Prevent Ice Dams on a Utah Roof</t>
+          <t>Can You Put a New Roof Over an Old Roof?</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr"/>
@@ -4979,69 +4979,207 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
+          <t>aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Aesthetic Roofing</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>South Jordan</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>What Causes Roof Leaks?</t>
+        </is>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>amcoroof.com</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>American Roofing Company</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>How to Prevent Ice Dams on a Utah Roof</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
           <t>roofamc.com</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Advanced Roofing &amp; Moisture Control</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/KtP6sjWjk6Nv9zaKZ4oPkH</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Anyone with the link</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>Premium redesign (v2) published 18 Oct</t>
         </is>
       </c>
-      <c r="J61" s="7" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>How Long Do Roofs Last in Utah?</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
+      <c r="L63" s="8" t="inlineStr">
         <is>
           <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofamc.com</t>
         </is>
       </c>
-      <c r="M61" s="7" t="inlineStr">
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr">
+      <c r="N63" s="7" t="inlineStr">
         <is>
           <t>phone and address format, blog author, "4th-generation" claim, forms need connecting.</t>
         </is>
       </c>
-      <c r="O61" s="7" t="inlineStr"/>
+      <c r="O63" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -5163,6 +5301,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$21</definedName>
   </definedNames>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -706,22 +706,22 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>anyandallservices.com</t>
+          <t>jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Any &amp; All Services</t>
+          <t>Jackson Family Plumbing &amp; HVAC</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
+          <t>https://claude.ai/artifact/CPRKjw5jkso5N8x2fxqYxi</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -744,30 +744,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>6 signs you need an electrician, according to NFPA</t>
+          <t>How to keep pipes from freezing (and what to do if they do)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live page is a "Colorado 24/7 Plumbing Call" template with no phone and nothing to recover (archive back to 2024 is the same). Built from the Google listing only: home + contact + 1 new post. Home targets "plumber west jordan" (630 words; no services, hours, licenses or rating invented)</t>
         </is>
       </c>
     </row>
@@ -777,22 +773,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>sterlingtreeco.godaddysites.com</t>
+          <t>dsihvac.com</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Sterling Tree Co.</t>
+          <t>Proformance Heating and Air</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
+          <t>https://claude.ai/artifact/AL6qDWamg184CgbJaLR3Db</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -802,7 +798,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -815,26 +811,30 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>Why topping hurts trees (and what arborists do instead)</t>
+          <t>How often to change your furnace filter (and what MERV rating to buy)</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\dsihvac.com</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business; CHECK FIRST: the domain and old site say "DSI HVAC", Google says Proformance (same phone number). Site down, so it was rebuilt from Internet Archive captures (Nov 2025 and Jan 2026): 7 pages at the same Wix URLs + 1 new post. Home targets "hvac company draper". DSI logo not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -844,22 +844,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>actionyardcare.com</t>
+          <t>marble-builders.com</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Action Lawn &amp; Yardcare</t>
+          <t>Marble Builders</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
+          <t>https://claude.ai/artifact/Q9dcVxd3VWZVsbNmCdKHfv</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -884,28 +884,28 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>How high should you mow a Utah lawn?</t>
+          <t>Lead paint and asbestos: what to know before remodeling an older home</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\marble-builders.com</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site suspended, so it was rebuilt from Internet Archive captures (Mar–Sep 2025): 60 pages at the same WordPress URLs + 1 new post. Home targets "general contractor riverton"; Three phone numbers (Google's 801-828-5540 used); copied "Marble Homes" FAQs removed; no project photos archived; 10 unrecoverable pages and the WordPress demo pages kept noindex; rating left out</t>
         </is>
       </c>
     </row>
@@ -915,22 +915,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>danielswildlife.com</t>
+          <t>prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Daniel's Wildlife &amp; Pest Control</t>
+          <t>Prestige Tree And Landscape</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
+          <t>https://claude.ai/artifact/WPVS4xgTgXQWwQDBK3atWJ</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -955,28 +955,28 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Found mouse droppings? How to clean up safely</t>
+          <t>How to mulch around trees (and why mulch volcanoes hurt them)</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 35 pages at the same .php URLs (site build writes real .php files) + 1 new post. Blank live home page replaced; home targets "tree service murray"; 1996 vs 1997 certification; WSJ/Disney claims and rating left out. Live backup files kept noindex (should be deleted)</t>
         </is>
       </c>
     </row>
@@ -986,22 +986,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>greenjanitorialservice.com</t>
+          <t>pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Green Janitorial Services</t>
+          <t>Pineapple Property Group</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
+          <t>https://claude.ai/artifact/R6DVER57ftYS7bXc55rs8e</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1024,26 +1024,30 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Is that cleaner really green? How to read eco labels</t>
+          <t>Fair housing basics every Salt Lake City landlord should know</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site blocks our network: built from Internet Archive captures (2025–2026). 10 pages at the same URLs (2 empty duplicates kept noindex) + 1 new post. Home targets "property management salt lake city", now one H1 (was 5). Their KPI and property-return figures kept and labelled as theirs; rating left out</t>
         </is>
       </c>
     </row>
@@ -1053,22 +1057,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>emetplumbingservices.com</t>
+          <t>whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Emet Plumbing Heating &amp; Air</t>
+          <t>White Pine Plumbing</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>South Jordan</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
+          <t>https://claude.ai/artifact/FXe8rjPexaoeJu8UMYx5Nm</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1093,28 +1097,28 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Furnace filters and MERV ratings, explained</t>
+          <t>Hard water and your plumbing: what it does and how to check yours</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (empty /blank/ becomes the blog index) + 1 new post. Home targets "plumber south jordan", now with one H1; Phone is a 435 number: copied exactly. Stock images not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -1124,22 +1128,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>everworklandscape.com</t>
+          <t>hvaccowboy.com</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Everwork Property Maintenance &amp; Landscaping</t>
+          <t>Cowboy Heating &amp; Air</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
+          <t>https://claude.ai/artifact/MC4t41ej3hDwZ5cSmFUf2K</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1162,30 +1166,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>How to water a Utah lawn: deeper, less often</t>
+          <t>Carbon monoxide and your furnace: what to know before winter</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\hvaccowboy.com</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site is a JavaScript app (search engines see 10 words): rebuilt as plain HTML (630 readable words) + 1 new post. Home targets "hvac company lehi"; Live schema says 3 reviews vs 162 on Google: rating left out. Award and Daikin/Bryant claims kept, to confirm</t>
         </is>
       </c>
     </row>
@@ -1195,22 +1195,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>iraut.com</t>
+          <t>anyandallservices.com</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Investment Realty Advisors</t>
+          <t>Any &amp; All Services</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
+          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1235,28 +1235,28 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>1031 exchange rules: what Utah real estate investors need to know</t>
+          <t>6 signs you need an electrician, according to NFPA</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>applianceserviceut.com</t>
+          <t>sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>ASI Appliance Services</t>
+          <t>Sterling Tree Co.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
+          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1304,30 +1304,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Clothes dryer fire safety: the lint habit that matters most</t>
+          <t>Why topping hurts trees (and what arborists do instead)</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -1337,22 +1333,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>triplejlandscaping.com</t>
+          <t>actionyardcare.com</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Triple J Landscaping</t>
+          <t>Action Lawn &amp; Yardcare</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
+          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1377,17 +1373,17 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>How much to water your lawn in Utah: the half-inch rule</t>
+          <t>How high should you mow a Utah lawn?</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1398,7 +1394,7 @@
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1404,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>joestreecareutah.com</t>
+          <t>danielswildlife.com</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Joe's Tree Care / Joe's Stump Grinding</t>
+          <t>Daniel's Wildlife &amp; Pest Control</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
+          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1448,17 +1444,17 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>How to water trees in Utah: deep, slow and less often</t>
+          <t>Found mouse droppings? How to clean up safely</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -1469,7 +1465,7 @@
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1475,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>utahbluechipcarpetcleaning.com</t>
+          <t>greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Blue Chip Carpet Cleaning</t>
+          <t>Green Janitorial Services</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
+          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1517,19 +1513,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
+          <t>Is that cleaner really green? How to read eco labels</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1540,7 +1532,7 @@
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -1550,22 +1542,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>trustyappliancerepairutah.com</t>
+          <t>emetplumbingservices.com</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Trusty Appliance Repair</t>
+          <t>Emet Plumbing Heating &amp; Air</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
+          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1590,17 +1582,17 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
+          <t>Furnace filters and MERV ratings, explained</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -1611,7 +1603,7 @@
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
         </is>
       </c>
     </row>
@@ -1621,22 +1613,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>vogldirect.com</t>
+          <t>everworklandscape.com</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Vogl Direct</t>
+          <t>Everwork Property Maintenance &amp; Landscaping</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Eagle Mountain</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
+          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1661,17 +1653,17 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
+          <t>How to water a Utah lawn: deeper, less often</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -1682,7 +1674,7 @@
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
         </is>
       </c>
     </row>
@@ -1692,22 +1684,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ahc-utah.com</t>
+          <t>iraut.com</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Affordable Heating &amp; Cooling</t>
+          <t>Investment Realty Advisors</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
+          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1732,17 +1724,17 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
+          <t>1031 exchange rules: what Utah real estate investors need to know</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -1753,7 +1745,7 @@
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1755,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>mountainwindowcleaning.com</t>
+          <t>applianceserviceut.com</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Mountain Window Cleaning</t>
+          <t>ASI Appliance Services</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
+          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1788,7 +1780,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -1803,28 +1795,28 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Why birds hit your windows, and how to stop it</t>
+          <t>Clothes dryer fire safety: the lint habit that matters most</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1826,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>rwkconstruction.com</t>
+          <t>triplejlandscaping.com</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>RWK Construction Co.</t>
+          <t>Triple J Landscaping</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Bluffdale</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
+          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1859,7 +1851,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1874,28 +1866,28 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
+          <t>How much to water your lawn in Utah: the half-inch rule</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1897,22 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>5starkb.com</t>
+          <t>joestreecareutah.com</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>5 Star Kitchen and Bath</t>
+          <t>Joe's Tree Care / Joe's Stump Grinding</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
+          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1930,7 +1922,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1945,28 +1937,28 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
+          <t>How to water trees in Utah: deep, slow and less often</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1968,32 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>acs-hoa.com</t>
+          <t>utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Advanced Community Services</t>
+          <t>Blue Chip Carpet Cleaning</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
+          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -2011,33 +2003,33 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>The HOA board's winter checklist for Utah communities</t>
+          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2039,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>equitypmusa.com</t>
+          <t>trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Equity Real Estate Property Management</t>
+          <t>Trusty Appliance Repair</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2062,17 +2054,17 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
+          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2082,33 +2074,33 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>How to spot a rental listing scam before you pay a dime</t>
+          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2110,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>abode.cleaning</t>
+          <t>vogldirect.com</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Abode House Cleaning</t>
+          <t>Vogl Direct</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Eagle Mountain</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
+          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2143,7 +2135,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -2158,28 +2150,28 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Cleaning products and the air in your home: a plain-language guide</t>
+          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -2189,32 +2181,32 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>lockthesmithut.com</t>
+          <t>ahc-utah.com</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Lockthesmith</t>
+          <t>Affordable Heating &amp; Cooling</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
+          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2224,33 +2216,33 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Hot cars and locked doors: what every Utah driver should know</t>
+          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2260,22 +2252,22 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>rasmussenlandscapes.com</t>
+          <t>mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Rasmussen Landscapes</t>
+          <t>Mountain Window Cleaning</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
+          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2300,17 +2292,17 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>When should you start watering your lawn in Utah?</t>
+          <t>Why birds hit your windows, and how to stop it</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -2321,7 +2313,7 @@
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2331,22 +2323,22 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ezelectric.com</t>
+          <t>rwkconstruction.com</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>EZ Electric</t>
+          <t>RWK Construction Co.</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Bluffdale</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
+          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2371,17 +2363,17 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
+          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -2392,7 +2384,7 @@
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2402,22 +2394,22 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>therepairpros.com</t>
+          <t>5starkb.com</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>The Repair Pros</t>
+          <t>5 Star Kitchen and Bath</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
+          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2442,17 +2434,17 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Repair or replace? How long appliances actually last</t>
+          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2463,7 +2455,7 @@
       <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
         </is>
       </c>
     </row>
@@ -2473,22 +2465,22 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>pestx.org</t>
+          <t>acs-hoa.com</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Pestx</t>
+          <t>Advanced Community Services</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
+          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2513,17 +2505,17 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
+          <t>The HOA board's winter checklist for Utah communities</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2534,7 +2526,7 @@
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
         </is>
       </c>
     </row>
@@ -2544,22 +2536,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>foundationrepairogden.com</t>
+          <t>equitypmusa.com</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Fortified Foundations</t>
+          <t>Equity Real Estate Property Management</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
+          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2569,7 +2561,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -2579,37 +2571,33 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
+          <t>How to spot a rental listing scam before you pay a dime</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
         </is>
       </c>
     </row>
@@ -2619,32 +2607,32 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>rhinofoundationsystems.com</t>
+          <t>abode.cleaning</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Rhino Foundation Systems</t>
+          <t>Abode House Cleaning</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>American Fork</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
+          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -2654,37 +2642,33 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
+          <t>Cleaning products and the air in your home: a plain-language guide</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2678,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>sandsroofingutah.com</t>
+          <t>lockthesmithut.com</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>S&amp;S Roofing, Inc.</t>
+          <t>Lockthesmith</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -2709,7 +2693,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
+          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2719,7 +2703,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -2729,37 +2713,33 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 20 Oct</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
+          <t>Hot cars and locked doors: what every Utah driver should know</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
         </is>
       </c>
     </row>
@@ -2769,32 +2749,32 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>stgeorgeconcreteleveling.com</t>
+          <t>rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>St. George Concrete Leveling</t>
+          <t>Rasmussen Landscapes</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
+          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -2804,37 +2784,33 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
+          <t>When should you start watering your lawn in Utah?</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
         </is>
       </c>
     </row>
@@ -2844,32 +2820,32 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>m3industriesconcrete.com</t>
+          <t>ezelectric.com</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>M3 Industries</t>
+          <t>EZ Electric</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
+          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -2879,37 +2855,33 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
+          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2891,32 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>thedisasterrepairteam.com</t>
+          <t>therepairpros.com</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Disaster Repair Team</t>
+          <t>The Repair Pros</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
+          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -2954,37 +2926,33 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
+          <t>Repair or replace? How long appliances actually last</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
-        <is>
-          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -2994,22 +2962,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>poly-lift.com</t>
+          <t>pestx.org</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Poly-Lift</t>
+          <t>Pestx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
+          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -3019,7 +2987,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -3029,37 +2997,33 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
+          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -3069,22 +3033,22 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>stgeorgehomeservices.com</t>
+          <t>foundationrepairogden.com</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>St. George Home Services</t>
+          <t>Fortified Foundations</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
+          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -3104,22 +3068,22 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
+          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -3129,12 +3093,12 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
+          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
+          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3108,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>cleartopsolutions.shop</t>
+          <t>rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>ClearTop Solutions</t>
+          <t>Rhino Foundation Systems</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>American Fork</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
+          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3179,22 +3143,22 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct)</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
+          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -3204,12 +3168,12 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
+          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
+          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
         </is>
       </c>
     </row>
@@ -3219,22 +3183,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>jsprofinish.com</t>
+          <t>sandsroofingutah.com</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>JS ProFinish</t>
+          <t>S&amp;S Roofing, Inc.</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Clearfield</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
+          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3254,22 +3218,22 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Premium redesign (v2) published 20 Oct</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
+          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -3279,12 +3243,12 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
+          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
+          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3258,12 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>armour-crete.com</t>
+          <t>stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Armour Crete</t>
+          <t>St. George Concrete Leveling</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -3309,7 +3273,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
+          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -3334,17 +3298,17 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
+          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -3354,12 +3318,12 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
+          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
+          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
         </is>
       </c>
     </row>
@@ -3369,22 +3333,22 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>swiftrestoreutah.com</t>
+          <t>m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Swift Restoration and Remodeling</t>
+          <t>M3 Industries</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
+          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -3407,15 +3371,19 @@
           <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -3425,12 +3393,12 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
+          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
+          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
         </is>
       </c>
     </row>
@@ -3440,22 +3408,22 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>exceptional-roofing.com</t>
+          <t>thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Exceptional Roofing</t>
+          <t>Disaster Repair Team</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
+          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3465,7 +3433,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -3475,22 +3443,22 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
+          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -3500,12 +3468,12 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
+          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
+          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
         </is>
       </c>
     </row>
@@ -3515,22 +3483,22 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>sfrutah.com</t>
+          <t>poly-lift.com</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Superior Foundation Repair Utah</t>
+          <t>Poly-Lift</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City &amp; St. George</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
+          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3540,7 +3508,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -3550,22 +3518,22 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
+          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -3575,12 +3543,12 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
+          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
+          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
         </is>
       </c>
     </row>
@@ -3590,22 +3558,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>dryhouse.com</t>
+          <t>stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Rocky Mountain Waterproofing</t>
+          <t>St. George Home Services</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
+          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3615,7 +3583,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -3625,18 +3593,22 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr"/>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
+          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -3646,12 +3618,12 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
+          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
+          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
         </is>
       </c>
     </row>
@@ -3661,22 +3633,22 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>davenportfoundationrepair.com</t>
+          <t>cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Davenport Foundation Repair</t>
+          <t>ClearTop Solutions</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
+          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3686,7 +3658,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3696,22 +3668,22 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
+          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3721,12 +3693,12 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
+          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
+          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
         </is>
       </c>
     </row>
@@ -3736,22 +3708,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>saltcityroofers.com</t>
+          <t>jsprofinish.com</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Salt City Roofers</t>
+          <t>JS ProFinish</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Clearfield</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
+          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3761,7 +3733,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3771,22 +3743,22 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
+          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3796,12 +3768,12 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
+          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
+          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3783,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>utahroofingpros.com</t>
+          <t>armour-crete.com</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Utah Roofing Pros</t>
+          <t>Armour Crete</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
+          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3836,7 +3808,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3846,22 +3818,22 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
+          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3871,12 +3843,12 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
+          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>The current city pages use AI-generated photos; none are used</t>
+          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
         </is>
       </c>
     </row>
@@ -3886,22 +3858,22 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>xperienceroofing.com</t>
+          <t>swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Xperience Roofing</t>
+          <t>Swift Restoration and Remodeling</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
+          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3911,7 +3883,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -3921,18 +3893,18 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr"/>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3942,12 +3914,12 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
+          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
+          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3929,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>utahoneroofing.com</t>
+          <t>exceptional-roofing.com</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Utah One Roofing / One Roofing LLC</t>
+          <t>Exceptional Roofing</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3972,7 +3944,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
+          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3982,7 +3954,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -3992,22 +3964,22 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
+          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -4017,12 +3989,12 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
+          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
+          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
         </is>
       </c>
     </row>
@@ -4032,22 +4004,22 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>roofrepairsaltlakecity.com</t>
+          <t>sfrutah.com</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Roof Repair Salt Lake City</t>
+          <t>Superior Foundation Repair Utah</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Salt Lake City &amp; St. George</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
+          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -4057,7 +4029,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -4067,18 +4039,22 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
+        </is>
+      </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -4088,12 +4064,12 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
+          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
         </is>
       </c>
     </row>
@@ -4103,22 +4079,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>skybridgeroofings.com</t>
+          <t>dryhouse.com</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Sky Bridge Roofing</t>
+          <t>Rocky Mountain Waterproofing</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
+          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -4128,7 +4104,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -4138,22 +4114,18 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct)</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Built premium from the start (19 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr"/>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
+          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4163,12 +4135,12 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
         </is>
       </c>
     </row>
@@ -4178,22 +4150,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>oakleyroofingslc.com</t>
+          <t>davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Oakley Roofing</t>
+          <t>Davenport Foundation Repair</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
+          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -4203,7 +4175,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -4213,22 +4185,22 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (17 Oct)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>514</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
+          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -4236,10 +4208,14 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
+        </is>
+      </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4225,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>mandmgutters.com</t>
+          <t>saltcityroofers.com</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>M&amp;M Gutters &amp; Exteriors</t>
+          <t>Salt City Roofers</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -4264,7 +4240,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
+          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -4274,7 +4250,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -4284,22 +4260,22 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
+          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4309,12 +4285,12 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
+          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
         </is>
       </c>
     </row>
@@ -4324,22 +4300,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>roofwiseut.com</t>
+          <t>utahroofingpros.com</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>RoofWise</t>
+          <t>Utah Roofing Pros</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
+          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -4349,7 +4325,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -4359,22 +4335,22 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>What Does Hail Damage Look Like on a Roof?</t>
+          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4384,12 +4360,12 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
+          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+          <t>The current city pages use AI-generated photos; none are used</t>
         </is>
       </c>
     </row>
@@ -4399,22 +4375,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>jordanriverroofing.com</t>
+          <t>xperienceroofing.com</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Jordan River Roofing</t>
+          <t>Xperience Roofing</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
+          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -4424,7 +4400,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -4434,22 +4410,18 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -4459,12 +4431,12 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4446,12 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>jemzaroofing.com</t>
+          <t>utahoneroofing.com</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Jemza Roofing</t>
+          <t>Utah One Roofing / One Roofing LLC</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -4489,7 +4461,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
+          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -4499,7 +4471,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -4509,22 +4481,22 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
+          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -4534,12 +4506,12 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
         </is>
       </c>
     </row>
@@ -4549,22 +4521,22 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>jandnroofing.com</t>
+          <t>roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>J &amp; N Roofing Maintenance, LLC</t>
+          <t>Roof Repair Salt Lake City</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
+          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -4574,7 +4546,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -4584,22 +4556,18 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>How Far Should Shingles Overhang the Drip Edge?</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4609,12 +4577,12 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
         </is>
       </c>
     </row>
@@ -4624,22 +4592,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>gprroofing.com</t>
+          <t>skybridgeroofings.com</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Go Pro Roofing</t>
+          <t>Sky Bridge Roofing</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -4649,7 +4617,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4659,22 +4627,22 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct)</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>How Are Valleys Done on a Metal Roof?</t>
+          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4684,10 +4652,14 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O56" s="7" t="inlineStr"/>
+          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -4695,22 +4667,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>pioneerroofingutah.com</t>
+          <t>oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Pioneer Roofing Co</t>
+          <t>Oakley Roofing</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, est. 1980</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -4730,22 +4702,22 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (17 Oct)</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
+          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4753,12 +4725,12 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -4766,22 +4738,22 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>ezroofingnow.com</t>
+          <t>mandmgutters.com</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>EZ Roofing</t>
+          <t>M&amp;M Gutters &amp; Exteriors</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4801,22 +4773,22 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>The Best Time of Year to Replace a Roof in Utah</t>
+          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -4826,10 +4798,14 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O58" s="7" t="inlineStr"/>
+          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -4837,22 +4813,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>customroofs.biz</t>
+          <t>roofwiseut.com</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Custom Roofing LLC</t>
+          <t>RoofWise</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -4872,22 +4848,22 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Why Does Copper Turn Green?</t>
+          <t>What Does Hail Damage Look Like on a Roof?</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -4897,10 +4873,14 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O59" s="7" t="inlineStr"/>
+          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -4908,22 +4888,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>aluminumlockroofing.com</t>
+          <t>jordanriverroofing.com</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Aluminum Lock Roofing</t>
+          <t>Jordan River Roofing</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4943,22 +4923,22 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Can You Put a New Roof Over an Old Roof?</t>
+          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -4968,10 +4948,14 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
-        </is>
-      </c>
-      <c r="O60" s="7" t="inlineStr"/>
+          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -4979,22 +4963,22 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>aestheticroofing.com</t>
+          <t>jemzaroofing.com</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Aesthetic Roofing</t>
+          <t>Jemza Roofing</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -5004,7 +4988,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -5019,17 +5003,17 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>What Causes Roof Leaks?</t>
+          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -5039,10 +5023,14 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
-        </is>
-      </c>
-      <c r="O61" s="7" t="inlineStr"/>
+          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -5050,18 +5038,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>amcoroof.com</t>
+          <t>jandnroofing.com</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>American Roofing Company</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr"/>
+          <t>J &amp; N Roofing Maintenance, LLC</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>West Valley City</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -5071,7 +5063,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -5086,17 +5078,17 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>How to Prevent Ice Dams on a Utah Roof</t>
+          <t>How Far Should Shingles Overhang the Drip Edge?</t>
         </is>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -5106,10 +5098,14 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
-        </is>
-      </c>
-      <c r="O62" s="7" t="inlineStr"/>
+          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -5117,69 +5113,562 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
+          <t>gprroofing.com</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Go Pro Roofing</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>West Valley City</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>How Are Valleys Done on a Metal Roof?</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>pioneerroofingutah.com</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Roofing Co</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, est. 1980</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>ezroofingnow.com</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>EZ Roofing</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>The Best Time of Year to Replace a Roof in Utah</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>customroofs.biz</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Custom Roofing LLC</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Lehi</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Why Does Copper Turn Green?</t>
+        </is>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>aluminumlockroofing.com</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Aluminum Lock Roofing</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Can You Put a New Roof Over an Old Roof?</t>
+        </is>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Aesthetic Roofing</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>South Jordan</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>What Causes Roof Leaks?</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>amcoroof.com</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>American Roofing Company</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>How to Prevent Ice Dams on a Utah Roof</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
           <t>roofamc.com</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Advanced Roofing &amp; Moisture Control</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/KtP6sjWjk6Nv9zaKZ4oPkH</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>Anyone with the link</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>Premium redesign (v2) published 18 Oct</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr">
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>How Long Do Roofs Last in Utah?</t>
         </is>
       </c>
-      <c r="L63" s="8" t="inlineStr">
+      <c r="L70" s="8" t="inlineStr">
         <is>
           <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofamc.com</t>
         </is>
       </c>
-      <c r="M63" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>phone and address format, blog author, "4th-generation" claim, forms need connecting.</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O63"/>
+  <autoFilter ref="A1:O70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -5305,6 +5794,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$21</definedName>
   </definedNames>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -706,22 +706,22 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>jacksonplumbinghvac.com</t>
+          <t>husky-property-maintenance</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Jackson Family Plumbing &amp; HVAC</t>
+          <t>Husky Property Maintenance</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/CPRKjw5jkso5N8x2fxqYxi</t>
+          <t>https://claude.ai/artifact/BuBpSuc9EUUCRroo3kpFWk</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -747,12 +747,12 @@
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>How to keep pipes from freezing (and what to do if they do)</t>
+          <t>Smoke and carbon monoxide alarms: where they go and how to keep them working</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\jacksonplumbinghvac.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\husky-property-maintenance</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -763,7 +763,7 @@
       <c r="N2" s="7" t="inlineStr"/>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; The live page is a "Colorado 24/7 Plumbing Call" template with no phone and nothing to recover (archive back to 2024 is the same). Built from the Google listing only: home + contact + 1 new post. Home targets "plumber west jordan" (630 words; no services, hours, licenses or rating invented)</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>dsihvac.com</t>
+          <t>superior-locksmith</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Proformance Heating and Air</t>
+          <t>Superior Locksmith</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AL6qDWamg184CgbJaLR3Db</t>
+          <t>https://claude.ai/artifact/HReg9oZJ3jAAfed8H76Uh4</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -811,19 +811,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>How often to change your furnace filter (and what MERV rating to buy)</t>
+          <t>Lock grades explained: what BHMA ratings actually test</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\dsihvac.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\superior-locksmith</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -834,7 +830,7 @@
       <c r="N3" s="7" t="inlineStr"/>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; CHECK FIRST: the domain and old site say "DSI HVAC", Google says Proformance (same phone number). Site down, so it was rebuilt from Internet Archive captures (Nov 2025 and Jan 2026): 7 pages at the same Wix URLs + 1 new post. Home targets "hvac company draper". DSI logo not used; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -844,22 +840,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>marble-builders.com</t>
+          <t>eagle-locksmith-inc</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Marble Builders</t>
+          <t>Eagle Locksmith inc</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Q9dcVxd3VWZVsbNmCdKHfv</t>
+          <t>https://claude.ai/artifact/SScjEhq4SK168TSnRkhRwi</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -882,19 +878,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="J4" s="7" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Lead paint and asbestos: what to know before remodeling an older home</t>
+          <t>How to hire a locksmith without getting scammed</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\marble-builders.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\eagle-locksmith-inc</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -905,7 +897,7 @@
       <c r="N4" s="7" t="inlineStr"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. Live site suspended, so it was rebuilt from Internet Archive captures (Mar–Sep 2025): 60 pages at the same WordPress URLs + 1 new post. Home targets "general contractor riverton"; Three phone numbers (Google's 801-828-5540 used); copied "Marble Homes" FAQs removed; no project photos archived; 10 unrecoverable pages and the WordPress demo pages kept noindex; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -915,22 +907,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>prestigetreeandlandscape.com</t>
+          <t>gross-family-plumbing-llc</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Prestige Tree And Landscape</t>
+          <t>Gross Family Plumbing LLC</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/WPVS4xgTgXQWwQDBK3atWJ</t>
+          <t>https://claude.ai/artifact/NrxzxVWua4DbfDr3dLBQXh</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -953,19 +945,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>How to mulch around trees (and why mulch volcanoes hurt them)</t>
+          <t>When to replace a toilet: what WaterSense says about old, thirsty models</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\prestigetreeandlandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\gross-family-plumbing-llc</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -976,7 +964,7 @@
       <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 35 pages at the same .php URLs (site build writes real .php files) + 1 new post. Blank live home page replaced; home targets "tree service murray"; 1996 vs 1997 certification; WSJ/Disney claims and rating left out. Live backup files kept noindex (should be deleted)</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -986,22 +974,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>pineapplepropertygroup.com</t>
+          <t>sean-s-plumbing</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Pineapple Property Group</t>
+          <t>Sean's Plumbing</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Jordan</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R6DVER57ftYS7bXc55rs8e</t>
+          <t>https://claude.ai/artifact/RdqdkJ3jEdsV7BjfDRCZNT</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1024,19 +1012,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Fair housing basics every Salt Lake City landlord should know</t>
+          <t>Hard water explained: what the numbers mean for your home</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pineapplepropertygroup.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sean-s-plumbing</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1047,7 +1031,7 @@
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site blocks our network: built from Internet Archive captures (2025–2026). 10 pages at the same URLs (2 empty duplicates kept noindex) + 1 new post. Home targets "property management salt lake city", now one H1 (was 5). Their KPI and property-return figures kept and labelled as theirs; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1041,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>whitepineplumbingut.com</t>
+          <t>stanley-sons-plumbing</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>White Pine Plumbing</t>
+          <t>Stanley &amp; Sons Plumbing</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/FXe8rjPexaoeJu8UMYx5Nm</t>
+          <t>https://claude.ai/artifact/QD8kCoiuwKcY88duh4Ubyk</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1082,7 +1066,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1095,30 +1079,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Hard water and your plumbing: what it does and how to check yours</t>
+          <t>What temperature should your water heater be? Why CPSC says 120F</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\whitepineplumbingut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stanley-sons-plumbing</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (empty /blank/ becomes the blog index) + 1 new post. Home targets "plumber south jordan", now with one H1; Phone is a 435 number: copied exactly. Stock images not used; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1128,22 +1108,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>hvaccowboy.com</t>
+          <t>stott-plumbing-excavating</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Cowboy Heating &amp; Air</t>
+          <t>Stott Plumbing &amp; Excavating</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MC4t41ej3hDwZ5cSmFUf2K</t>
+          <t>https://claude.ai/artifact/EqSWC3Wsfpbwkrt8jvzoA3</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1153,7 +1133,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1169,23 +1149,23 @@
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide and your furnace: what to know before winter</t>
+          <t>Blue Stakes 811 in Utah: what to know before you dig</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\hvaccowboy.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stott-plumbing-excavating</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. Live site is a JavaScript app (search engines see 10 words): rebuilt as plain HTML (630 readable words) + 1 new post. Home targets "hvac company lehi"; Live schema says 3 reviews vs 162 on Google: rating left out. Award and Daikin/Bryant claims kept, to confirm</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1195,22 +1175,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>anyandallservices.com</t>
+          <t>conrad-s-roofing-construction</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Any &amp; All Services</t>
+          <t>Conrad's Roofing &amp; Construction</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
+          <t>https://claude.ai/artifact/YQJ3JwkvSt8jQ8gxkA3UgK</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1220,7 +1200,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1233,30 +1213,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>6 signs you need an electrician, according to NFPA</t>
+          <t>How much snow can a roof hold? Weights, warning signs and safe removal</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\conrad-s-roofing-construction</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1266,22 +1242,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>sterlingtreeco.godaddysites.com</t>
+          <t>rooftek</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Sterling Tree Co.</t>
+          <t>RoofTek</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Millcreek</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
+          <t>https://claude.ai/artifact/AFRtanAgbrhxQxNHmB1ZTX</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1291,7 +1267,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1307,23 +1283,23 @@
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Why topping hurts trees (and what arborists do instead)</t>
+          <t>What is a FORTIFIED roof? A homeowner's guide to the IBHS standard</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rooftek</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1333,22 +1309,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>actionyardcare.com</t>
+          <t>jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Action Lawn &amp; Yardcare</t>
+          <t>Jackson Family Plumbing &amp; HVAC</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
+          <t>https://claude.ai/artifact/CPRKjw5jkso5N8x2fxqYxi</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1358,7 +1334,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1371,30 +1347,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>How high should you mow a Utah lawn?</t>
+          <t>How to keep pipes from freezing (and what to do if they do)</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live page is a "Colorado 24/7 Plumbing Call" template with no phone and nothing to recover (archive back to 2024 is the same). Built from the Google listing only: home + contact + 1 new post. Home targets "plumber west jordan" (630 words; no services, hours, licenses or rating invented)</t>
         </is>
       </c>
     </row>
@@ -1404,22 +1376,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>danielswildlife.com</t>
+          <t>dsihvac.com</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Daniel's Wildlife &amp; Pest Control</t>
+          <t>Proformance Heating and Air</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
+          <t>https://claude.ai/artifact/AL6qDWamg184CgbJaLR3Db</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1429,7 +1401,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1444,28 +1416,28 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Found mouse droppings? How to clean up safely</t>
+          <t>How often to change your furnace filter (and what MERV rating to buy)</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\dsihvac.com</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; CHECK FIRST: the domain and old site say "DSI HVAC", Google says Proformance (same phone number). Site down, so it was rebuilt from Internet Archive captures (Nov 2025 and Jan 2026): 7 pages at the same Wix URLs + 1 new post. Home targets "hvac company draper". DSI logo not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -1475,22 +1447,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>greenjanitorialservice.com</t>
+          <t>marble-builders.com</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Green Janitorial Services</t>
+          <t>Marble Builders</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
+          <t>https://claude.ai/artifact/Q9dcVxd3VWZVsbNmCdKHfv</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1500,7 +1472,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1513,26 +1485,30 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Is that cleaner really green? How to read eco labels</t>
+          <t>Lead paint and asbestos: what to know before remodeling an older home</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\marble-builders.com</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site suspended, so it was rebuilt from Internet Archive captures (Mar–Sep 2025): 60 pages at the same WordPress URLs + 1 new post. Home targets "general contractor riverton"; Three phone numbers (Google's 801-828-5540 used); copied "Marble Homes" FAQs removed; no project photos archived; 10 unrecoverable pages and the WordPress demo pages kept noindex; rating left out</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1518,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>emetplumbingservices.com</t>
+          <t>prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Emet Plumbing Heating &amp; Air</t>
+          <t>Prestige Tree And Landscape</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
+          <t>https://claude.ai/artifact/WPVS4xgTgXQWwQDBK3atWJ</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1567,7 +1543,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1582,28 +1558,28 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Furnace filters and MERV ratings, explained</t>
+          <t>How to mulch around trees (and why mulch volcanoes hurt them)</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 35 pages at the same .php URLs (site build writes real .php files) + 1 new post. Blank live home page replaced; home targets "tree service murray"; 1996 vs 1997 certification; WSJ/Disney claims and rating left out. Live backup files kept noindex (should be deleted)</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1589,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>everworklandscape.com</t>
+          <t>pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Everwork Property Maintenance &amp; Landscaping</t>
+          <t>Pineapple Property Group</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
+          <t>https://claude.ai/artifact/R6DVER57ftYS7bXc55rs8e</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1638,7 +1614,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1653,28 +1629,28 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>How to water a Utah lawn: deeper, less often</t>
+          <t>Fair housing basics every Salt Lake City landlord should know</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site blocks our network: built from Internet Archive captures (2025–2026). 10 pages at the same URLs (2 empty duplicates kept noindex) + 1 new post. Home targets "property management salt lake city", now one H1 (was 5). Their KPI and property-return figures kept and labelled as theirs; rating left out</t>
         </is>
       </c>
     </row>
@@ -1684,22 +1660,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>iraut.com</t>
+          <t>whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Investment Realty Advisors</t>
+          <t>White Pine Plumbing</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>South Jordan</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
+          <t>https://claude.ai/artifact/FXe8rjPexaoeJu8UMYx5Nm</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1724,28 +1700,28 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>1031 exchange rules: what Utah real estate investors need to know</t>
+          <t>Hard water and your plumbing: what it does and how to check yours</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (empty /blank/ becomes the blog index) + 1 new post. Home targets "plumber south jordan", now with one H1; Phone is a 435 number: copied exactly. Stock images not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1731,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>applianceserviceut.com</t>
+          <t>hvaccowboy.com</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ASI Appliance Services</t>
+          <t>Cowboy Heating &amp; Air</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
+          <t>https://claude.ai/artifact/MC4t41ej3hDwZ5cSmFUf2K</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1793,30 +1769,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Clothes dryer fire safety: the lint habit that matters most</t>
+          <t>Carbon monoxide and your furnace: what to know before winter</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\hvaccowboy.com</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site is a JavaScript app (search engines see 10 words): rebuilt as plain HTML (630 readable words) + 1 new post. Home targets "hvac company lehi"; Live schema says 3 reviews vs 162 on Google: rating left out. Award and Daikin/Bryant claims kept, to confirm</t>
         </is>
       </c>
     </row>
@@ -1826,22 +1798,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>triplejlandscaping.com</t>
+          <t>anyandallservices.com</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Triple J Landscaping</t>
+          <t>Any &amp; All Services</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
+          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1866,28 +1838,28 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>How much to water your lawn in Utah: the half-inch rule</t>
+          <t>6 signs you need an electrician, according to NFPA</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1869,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>joestreecareutah.com</t>
+          <t>sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Joe's Tree Care / Joe's Stump Grinding</t>
+          <t>Sterling Tree Co.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1912,7 +1884,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
+          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1935,30 +1907,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>How to water trees in Utah: deep, slow and less often</t>
+          <t>Why topping hurts trees (and what arborists do instead)</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -1968,22 +1936,22 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>utahbluechipcarpetcleaning.com</t>
+          <t>actionyardcare.com</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Blue Chip Carpet Cleaning</t>
+          <t>Action Lawn &amp; Yardcare</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
+          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2008,17 +1976,17 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
+          <t>How high should you mow a Utah lawn?</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -2029,7 +1997,7 @@
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
         </is>
       </c>
     </row>
@@ -2039,22 +2007,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>trustyappliancerepairutah.com</t>
+          <t>danielswildlife.com</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Trusty Appliance Repair</t>
+          <t>Daniel's Wildlife &amp; Pest Control</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
+          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2079,17 +2047,17 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
+          <t>Found mouse droppings? How to clean up safely</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -2100,7 +2068,7 @@
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2078,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>vogldirect.com</t>
+          <t>greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Vogl Direct</t>
+          <t>Green Janitorial Services</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Eagle Mountain</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
+          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2148,19 +2116,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="J22" s="7" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
+          <t>Is that cleaner really green? How to read eco labels</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2171,7 +2135,7 @@
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -2181,22 +2145,22 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ahc-utah.com</t>
+          <t>emetplumbingservices.com</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Affordable Heating &amp; Cooling</t>
+          <t>Emet Plumbing Heating &amp; Air</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
+          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2221,17 +2185,17 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
+          <t>Furnace filters and MERV ratings, explained</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -2242,7 +2206,7 @@
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2216,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>mountainwindowcleaning.com</t>
+          <t>everworklandscape.com</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Mountain Window Cleaning</t>
+          <t>Everwork Property Maintenance &amp; Landscaping</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -2267,7 +2231,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
+          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2277,7 +2241,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -2292,28 +2256,28 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Why birds hit your windows, and how to stop it</t>
+          <t>How to water a Utah lawn: deeper, less often</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
         </is>
       </c>
     </row>
@@ -2323,22 +2287,22 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>rwkconstruction.com</t>
+          <t>iraut.com</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>RWK Construction Co.</t>
+          <t>Investment Realty Advisors</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Bluffdale</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
+          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2348,7 +2312,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -2363,28 +2327,28 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
+          <t>1031 exchange rules: what Utah real estate investors need to know</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2358,22 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>5starkb.com</t>
+          <t>applianceserviceut.com</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>5 Star Kitchen and Bath</t>
+          <t>ASI Appliance Services</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
+          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2419,7 +2383,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -2434,28 +2398,28 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
+          <t>Clothes dryer fire safety: the lint habit that matters most</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
         </is>
       </c>
     </row>
@@ -2465,32 +2429,32 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>acs-hoa.com</t>
+          <t>triplejlandscaping.com</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Advanced Community Services</t>
+          <t>Triple J Landscaping</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
+          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -2500,33 +2464,33 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>The HOA board's winter checklist for Utah communities</t>
+          <t>How much to water your lawn in Utah: the half-inch rule</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
         </is>
       </c>
     </row>
@@ -2536,32 +2500,32 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>equitypmusa.com</t>
+          <t>joestreecareutah.com</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Equity Real Estate Property Management</t>
+          <t>Joe's Tree Care / Joe's Stump Grinding</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
+          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -2571,33 +2535,33 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>How to spot a rental listing scam before you pay a dime</t>
+          <t>How to water trees in Utah: deep, slow and less often</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
         </is>
       </c>
     </row>
@@ -2607,22 +2571,22 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>abode.cleaning</t>
+          <t>utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Abode House Cleaning</t>
+          <t>Blue Chip Carpet Cleaning</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
+          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2632,7 +2596,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -2647,28 +2611,28 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Cleaning products and the air in your home: a plain-language guide</t>
+          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
         </is>
       </c>
     </row>
@@ -2678,32 +2642,32 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>lockthesmithut.com</t>
+          <t>trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Lockthesmith</t>
+          <t>Trusty Appliance Repair</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
+          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -2713,33 +2677,33 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Hot cars and locked doors: what every Utah driver should know</t>
+          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
         </is>
       </c>
     </row>
@@ -2749,22 +2713,22 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>rasmussenlandscapes.com</t>
+          <t>vogldirect.com</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Rasmussen Landscapes</t>
+          <t>Vogl Direct</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Eagle Mountain</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
+          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2774,7 +2738,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -2789,28 +2753,28 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>When should you start watering your lawn in Utah?</t>
+          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2784,12 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>ezelectric.com</t>
+          <t>ahc-utah.com</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>EZ Electric</t>
+          <t>Affordable Heating &amp; Cooling</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -2835,7 +2799,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
+          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2845,7 +2809,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -2860,28 +2824,28 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
+          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2855,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>therepairpros.com</t>
+          <t>mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>The Repair Pros</t>
+          <t>Mountain Window Cleaning</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
+          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2931,17 +2895,17 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Repair or replace? How long appliances actually last</t>
+          <t>Why birds hit your windows, and how to stop it</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -2952,7 +2916,7 @@
       <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2962,27 +2926,27 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>pestx.org</t>
+          <t>rwkconstruction.com</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Pestx</t>
+          <t>RWK Construction Co.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Bluffdale</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
+          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -2997,22 +2961,22 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
+          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -3023,7 +2987,7 @@
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -3033,32 +2997,32 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>foundationrepairogden.com</t>
+          <t>5starkb.com</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Fortified Foundations</t>
+          <t>5 Star Kitchen and Bath</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
+          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -3068,37 +3032,33 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
+          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
         </is>
       </c>
     </row>
@@ -3108,22 +3068,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>rhinofoundationsystems.com</t>
+          <t>acs-hoa.com</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Rhino Foundation Systems</t>
+          <t>Advanced Community Services</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>American Fork</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
+          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -3143,37 +3103,33 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
+          <t>The HOA board's winter checklist for Utah communities</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
         </is>
       </c>
     </row>
@@ -3183,22 +3139,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>sandsroofingutah.com</t>
+          <t>equitypmusa.com</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>S&amp;S Roofing, Inc.</t>
+          <t>Equity Real Estate Property Management</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
+          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3208,7 +3164,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -3218,37 +3174,33 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 20 Oct</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
+          <t>How to spot a rental listing scam before you pay a dime</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
         </is>
       </c>
     </row>
@@ -3258,32 +3210,32 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>stgeorgeconcreteleveling.com</t>
+          <t>abode.cleaning</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>St. George Concrete Leveling</t>
+          <t>Abode House Cleaning</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
+          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -3293,37 +3245,33 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
+          <t>Cleaning products and the air in your home: a plain-language guide</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
         </is>
       </c>
     </row>
@@ -3333,22 +3281,22 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>m3industriesconcrete.com</t>
+          <t>lockthesmithut.com</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>M3 Industries</t>
+          <t>Lockthesmith</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
+          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -3358,7 +3306,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -3368,37 +3316,33 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
+          <t>Hot cars and locked doors: what every Utah driver should know</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr"/>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
         </is>
       </c>
     </row>
@@ -3408,32 +3352,32 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>thedisasterrepairteam.com</t>
+          <t>rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Disaster Repair Team</t>
+          <t>Rasmussen Landscapes</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
+          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -3443,37 +3387,33 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
+          <t>When should you start watering your lawn in Utah?</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr"/>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
         </is>
       </c>
     </row>
@@ -3483,32 +3423,32 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>poly-lift.com</t>
+          <t>ezelectric.com</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Poly-Lift</t>
+          <t>EZ Electric</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
+          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -3518,37 +3458,33 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
+          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="inlineStr">
-        <is>
-          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3494,32 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>stgeorgehomeservices.com</t>
+          <t>therepairpros.com</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>St. George Home Services</t>
+          <t>The Repair Pros</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
+          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -3593,37 +3529,33 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
+          <t>Repair or replace? How long appliances actually last</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -3633,22 +3565,22 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>cleartopsolutions.shop</t>
+          <t>pestx.org</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ClearTop Solutions</t>
+          <t>Pestx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
+          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3658,7 +3590,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3668,37 +3600,33 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
+          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -3708,22 +3636,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>jsprofinish.com</t>
+          <t>foundationrepairogden.com</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>JS ProFinish</t>
+          <t>Fortified Foundations</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Clearfield</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
+          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3743,22 +3671,22 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
+          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3768,12 +3696,12 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
+          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
+          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
         </is>
       </c>
     </row>
@@ -3783,22 +3711,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>armour-crete.com</t>
+          <t>rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Armour Crete</t>
+          <t>Rhino Foundation Systems</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>American Fork</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
+          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3818,22 +3746,22 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct)</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
+          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3843,12 +3771,12 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
+          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
+          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
         </is>
       </c>
     </row>
@@ -3858,22 +3786,22 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>swiftrestoreutah.com</t>
+          <t>sandsroofingutah.com</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Swift Restoration and Remodeling</t>
+          <t>S&amp;S Roofing, Inc.</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
+          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3893,18 +3821,22 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr"/>
+          <t>Premium redesign (v2) published 20 Oct</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3914,12 +3846,12 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
+          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
+          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
         </is>
       </c>
     </row>
@@ -3929,22 +3861,22 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>exceptional-roofing.com</t>
+          <t>stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Exceptional Roofing</t>
+          <t>St. George Concrete Leveling</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
+          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3954,7 +3886,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -3964,22 +3896,22 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
+          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -3989,12 +3921,12 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
+          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
+          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
         </is>
       </c>
     </row>
@@ -4004,22 +3936,22 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>sfrutah.com</t>
+          <t>m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Superior Foundation Repair Utah</t>
+          <t>M3 Industries</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City &amp; St. George</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
+          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -4029,7 +3961,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -4039,22 +3971,22 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
+          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -4064,12 +3996,12 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
+          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
+          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
         </is>
       </c>
     </row>
@@ -4079,22 +4011,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>dryhouse.com</t>
+          <t>thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Rocky Mountain Waterproofing</t>
+          <t>Disaster Repair Team</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
+          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -4104,7 +4036,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -4114,18 +4046,22 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr"/>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
+          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4135,12 +4071,12 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
+          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
+          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
         </is>
       </c>
     </row>
@@ -4150,22 +4086,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>davenportfoundationrepair.com</t>
+          <t>poly-lift.com</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Davenport Foundation Repair</t>
+          <t>Poly-Lift</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
+          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -4175,7 +4111,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -4185,22 +4121,22 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
+          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -4210,12 +4146,12 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
+          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
+          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
         </is>
       </c>
     </row>
@@ -4225,22 +4161,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>saltcityroofers.com</t>
+          <t>stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Salt City Roofers</t>
+          <t>St. George Home Services</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
+          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -4250,7 +4186,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -4260,22 +4196,22 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
+          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4285,12 +4221,12 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
+          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
+          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
         </is>
       </c>
     </row>
@@ -4300,22 +4236,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>utahroofingpros.com</t>
+          <t>cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Utah Roofing Pros</t>
+          <t>ClearTop Solutions</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
+          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -4325,7 +4261,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -4335,22 +4271,22 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
+          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4360,12 +4296,12 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
+          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>The current city pages use AI-generated photos; none are used</t>
+          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4311,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>xperienceroofing.com</t>
+          <t>jsprofinish.com</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Xperience Roofing</t>
+          <t>JS ProFinish</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Clearfield</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
+          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -4400,7 +4336,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -4410,18 +4346,22 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
+        </is>
+      </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -4431,12 +4371,12 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
+          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
+          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4386,22 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>utahoneroofing.com</t>
+          <t>armour-crete.com</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Utah One Roofing / One Roofing LLC</t>
+          <t>Armour Crete</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
+          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -4471,7 +4411,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -4481,22 +4421,22 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
+          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -4506,12 +4446,12 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
+          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
+          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4461,22 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>roofrepairsaltlakecity.com</t>
+          <t>swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Roof Repair Salt Lake City</t>
+          <t>Swift Restoration and Remodeling</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
+          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -4546,7 +4486,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -4556,18 +4496,18 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr"/>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+        </is>
+      </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4577,12 +4517,12 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
+          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
         </is>
       </c>
     </row>
@@ -4592,22 +4532,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>skybridgeroofings.com</t>
+          <t>exceptional-roofing.com</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Sky Bridge Roofing</t>
+          <t>Exceptional Roofing</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
+          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -4617,7 +4557,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4627,22 +4567,22 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
+          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4652,12 +4592,12 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4607,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>oakleyroofingslc.com</t>
+          <t>sfrutah.com</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Oakley Roofing</t>
+          <t>Superior Foundation Repair Utah</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Salt Lake City &amp; St. George</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
+          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -4692,7 +4632,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -4702,22 +4642,22 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (17 Oct)</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
+          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4725,10 +4665,14 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
+        </is>
+      </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
         </is>
       </c>
     </row>
@@ -4738,22 +4682,22 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>mandmgutters.com</t>
+          <t>dryhouse.com</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>M&amp;M Gutters &amp; Exteriors</t>
+          <t>Rocky Mountain Waterproofing</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
+          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4763,7 +4707,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -4773,22 +4717,18 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
+          <t>Built premium from the start (19 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr"/>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
+          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -4798,12 +4738,12 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
+          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
         </is>
       </c>
     </row>
@@ -4813,22 +4753,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>roofwiseut.com</t>
+          <t>davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>RoofWise</t>
+          <t>Davenport Foundation Repair</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
+          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -4838,7 +4778,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -4848,22 +4788,22 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>514</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>What Does Hail Damage Look Like on a Roof?</t>
+          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -4873,12 +4813,12 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
+          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
         </is>
       </c>
     </row>
@@ -4888,22 +4828,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>jordanriverroofing.com</t>
+          <t>saltcityroofers.com</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Jordan River Roofing</t>
+          <t>Salt City Roofers</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
+          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4913,7 +4853,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -4923,22 +4863,22 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
+          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -4948,12 +4888,12 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
         </is>
       </c>
     </row>
@@ -4963,22 +4903,22 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>jemzaroofing.com</t>
+          <t>utahroofingpros.com</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Jemza Roofing</t>
+          <t>Utah Roofing Pros</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
+          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -4988,7 +4928,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4998,22 +4938,22 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
+          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -5023,12 +4963,12 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+          <t>The current city pages use AI-generated photos; none are used</t>
         </is>
       </c>
     </row>
@@ -5038,22 +4978,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>jandnroofing.com</t>
+          <t>xperienceroofing.com</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>J &amp; N Roofing Maintenance, LLC</t>
+          <t>Xperience Roofing</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
+          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -5063,7 +5003,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -5073,22 +5013,18 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>How Far Should Shingles Overhang the Drip Edge?</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -5098,12 +5034,12 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
         </is>
       </c>
     </row>
@@ -5113,22 +5049,22 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>gprroofing.com</t>
+          <t>utahoneroofing.com</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Go Pro Roofing</t>
+          <t>Utah One Roofing / One Roofing LLC</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -5138,7 +5074,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -5148,22 +5084,22 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>How Are Valleys Done on a Metal Roof?</t>
+          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
         </is>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -5173,10 +5109,14 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O63" s="7" t="inlineStr"/>
+          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -5184,22 +5124,22 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>pioneerroofingutah.com</t>
+          <t>roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Pioneer Roofing Co</t>
+          <t>Roof Repair Salt Lake City</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, est. 1980</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -5209,7 +5149,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -5219,22 +5159,18 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr"/>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -5244,10 +5180,14 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O64" s="7" t="inlineStr"/>
+          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5255,22 +5195,22 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>ezroofingnow.com</t>
+          <t>skybridgeroofings.com</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>EZ Roofing</t>
+          <t>Sky Bridge Roofing</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -5280,7 +5220,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -5290,22 +5230,22 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (18 Oct)</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>The Best Time of Year to Replace a Roof in Utah</t>
+          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
         </is>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -5315,10 +5255,14 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O65" s="7" t="inlineStr"/>
+          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -5326,22 +5270,22 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>customroofs.biz</t>
+          <t>oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Custom Roofing LLC</t>
+          <t>Oakley Roofing</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -5361,22 +5305,22 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Built premium from the start (17 Oct)</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>Why Does Copper Turn Green?</t>
+          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -5384,12 +5328,12 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr">
-        <is>
-          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr"/>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -5397,12 +5341,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>aluminumlockroofing.com</t>
+          <t>mandmgutters.com</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Aluminum Lock Roofing</t>
+          <t>M&amp;M Gutters &amp; Exteriors</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -5412,7 +5356,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -5432,22 +5376,22 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Can You Put a New Roof Over an Old Roof?</t>
+          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -5457,10 +5401,14 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
-        </is>
-      </c>
-      <c r="O67" s="7" t="inlineStr"/>
+          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -5468,22 +5416,22 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>aestheticroofing.com</t>
+          <t>roofwiseut.com</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Aesthetic Roofing</t>
+          <t>RoofWise</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -5493,7 +5441,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -5503,22 +5451,22 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>What Causes Roof Leaks?</t>
+          <t>What Does Hail Damage Look Like on a Roof?</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -5528,10 +5476,14 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
-        </is>
-      </c>
-      <c r="O68" s="7" t="inlineStr"/>
+          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -5539,18 +5491,22 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>amcoroof.com</t>
+          <t>jordanriverroofing.com</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>American Roofing Company</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
+          <t>Jordan River Roofing</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Taylorsville</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -5560,7 +5516,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -5570,22 +5526,22 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>How to Prevent Ice Dams on a Utah Roof</t>
+          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -5595,10 +5551,14 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
-        </is>
-      </c>
-      <c r="O69" s="7" t="inlineStr"/>
+          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -5606,69 +5566,712 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
+          <t>jemzaroofing.com</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Jemza Roofing</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>jandnroofing.com</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>J &amp; N Roofing Maintenance, LLC</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>West Valley City</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>How Far Should Shingles Overhang the Drip Edge?</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>gprroofing.com</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Go Pro Roofing</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>West Valley City</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>How Are Valleys Done on a Metal Roof?</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>pioneerroofingutah.com</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Roofing Co</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, est. 1980</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>ezroofingnow.com</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>EZ Roofing</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>The Best Time of Year to Replace a Roof in Utah</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>customroofs.biz</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Custom Roofing LLC</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Lehi</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Why Does Copper Turn Green?</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>aluminumlockroofing.com</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Aluminum Lock Roofing</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>Can You Put a New Roof Over an Old Roof?</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Aesthetic Roofing</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>South Jordan</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>What Causes Roof Leaks?</t>
+        </is>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>amcoroof.com</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>American Roofing Company</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>How to Prevent Ice Dams on a Utah Roof</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
           <t>roofamc.com</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Advanced Roofing &amp; Moisture Control</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/KtP6sjWjk6Nv9zaKZ4oPkH</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Anyone with the link</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Premium redesign (v2) published 18 Oct</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>How Long Do Roofs Last in Utah?</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr">
+      <c r="L79" s="8" t="inlineStr">
         <is>
           <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofamc.com</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>phone and address format, blog author, "4th-generation" claim, forms need connecting.</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr"/>
+      <c r="O79" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O70"/>
+  <autoFilter ref="A1:O79"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -5808,6 +6411,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redesigns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports only" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Redesigns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reports only" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$79</definedName>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Redesigns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Reports only" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redesigns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports only" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$79</definedName>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026</t>
+          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed</t>
         </is>
       </c>
     </row>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed</t>
+          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
         </is>
       </c>
     </row>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Older previews" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -706,32 +706,32 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>husky-property-maintenance</t>
+          <t>earthenphoenix.com</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Husky Property Maintenance</t>
+          <t>Earthen Phoenix</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Massage, Yoga &amp; Reiki, Salt Lake City</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/BuBpSuc9EUUCRroo3kpFWk</t>
+          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link)</t>
+          <t>Private until shared (open the link, Share, Anyone with the link). The older home-page link (Jsn9NFxJmciVtundmDbW7H) is public and was not changed.</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>30 Oct 2026</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -741,31 +741,27 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (21 Oct)</t>
+          <t>Full 17-page site with per-service animations (30 Oct)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>Smoke and carbon monoxide alarms: where they go and how to keep them working</t>
-        </is>
-      </c>
+      <c r="K2" s="7" t="inlineStr"/>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\husky-property-maintenance</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\earthenphoenix.com\2026-10-30_earthenphoenix.com_full-site-preview</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
-        </is>
-      </c>
+          <t>Checked 30 Oct (menu panel under header, header pinned after scroll, scrolled header colours)</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>client: yoga price ($140 or $120), whether to show the street address and hours, more session photos, OK to reuse the 3 testimonials; developer: move the GHL booking calendar before launch</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -773,22 +769,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>superior-locksmith</t>
+          <t>husky-property-maintenance</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Superior Locksmith</t>
+          <t>Husky Property Maintenance</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/HReg9oZJ3jAAfed8H76Uh4</t>
+          <t>https://claude.ai/artifact/BuBpSuc9EUUCRroo3kpFWk</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -814,12 +810,12 @@
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>Lock grades explained: what BHMA ratings actually test</t>
+          <t>Smoke and carbon monoxide alarms: where they go and how to keep them working</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\superior-locksmith</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\husky-property-maintenance</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -840,22 +836,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>eagle-locksmith-inc</t>
+          <t>superior-locksmith</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Eagle Locksmith inc</t>
+          <t>Superior Locksmith</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/SScjEhq4SK168TSnRkhRwi</t>
+          <t>https://claude.ai/artifact/HReg9oZJ3jAAfed8H76Uh4</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -881,12 +877,12 @@
       <c r="J4" s="7" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>How to hire a locksmith without getting scammed</t>
+          <t>Lock grades explained: what BHMA ratings actually test</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\eagle-locksmith-inc</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\superior-locksmith</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -907,12 +903,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>gross-family-plumbing-llc</t>
+          <t>eagle-locksmith-inc</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Gross Family Plumbing LLC</t>
+          <t>Eagle Locksmith inc</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -922,7 +918,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NrxzxVWua4DbfDr3dLBQXh</t>
+          <t>https://claude.ai/artifact/SScjEhq4SK168TSnRkhRwi</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -948,12 +944,12 @@
       <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>When to replace a toilet: what WaterSense says about old, thirsty models</t>
+          <t>How to hire a locksmith without getting scammed</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\gross-family-plumbing-llc</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\eagle-locksmith-inc</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -974,22 +970,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>sean-s-plumbing</t>
+          <t>gross-family-plumbing-llc</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Sean's Plumbing</t>
+          <t>Gross Family Plumbing LLC</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RdqdkJ3jEdsV7BjfDRCZNT</t>
+          <t>https://claude.ai/artifact/NrxzxVWua4DbfDr3dLBQXh</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1015,12 +1011,12 @@
       <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Hard water explained: what the numbers mean for your home</t>
+          <t>When to replace a toilet: what WaterSense says about old, thirsty models</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sean-s-plumbing</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\gross-family-plumbing-llc</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1041,22 +1037,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>stanley-sons-plumbing</t>
+          <t>sean-s-plumbing</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Stanley &amp; Sons Plumbing</t>
+          <t>Sean's Plumbing</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Jordan</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QD8kCoiuwKcY88duh4Ubyk</t>
+          <t>https://claude.ai/artifact/RdqdkJ3jEdsV7BjfDRCZNT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1082,12 +1078,12 @@
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>What temperature should your water heater be? Why CPSC says 120F</t>
+          <t>Hard water explained: what the numbers mean for your home</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stanley-sons-plumbing</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sean-s-plumbing</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1108,12 +1104,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>stott-plumbing-excavating</t>
+          <t>stanley-sons-plumbing</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Stott Plumbing &amp; Excavating</t>
+          <t>Stanley &amp; Sons Plumbing</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1123,7 +1119,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EqSWC3Wsfpbwkrt8jvzoA3</t>
+          <t>https://claude.ai/artifact/QD8kCoiuwKcY88duh4Ubyk</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1149,12 +1145,12 @@
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Blue Stakes 811 in Utah: what to know before you dig</t>
+          <t>What temperature should your water heater be? Why CPSC says 120F</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stott-plumbing-excavating</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stanley-sons-plumbing</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -1175,22 +1171,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>conrad-s-roofing-construction</t>
+          <t>stott-plumbing-excavating</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Conrad's Roofing &amp; Construction</t>
+          <t>Stott Plumbing &amp; Excavating</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/YQJ3JwkvSt8jQ8gxkA3UgK</t>
+          <t>https://claude.ai/artifact/EqSWC3Wsfpbwkrt8jvzoA3</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1216,12 +1212,12 @@
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>How much snow can a roof hold? Weights, warning signs and safe removal</t>
+          <t>Blue Stakes 811 in Utah: what to know before you dig</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\conrad-s-roofing-construction</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\stott-plumbing-excavating</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -1242,22 +1238,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>rooftek</t>
+          <t>conrad-s-roofing-construction</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>RoofTek</t>
+          <t>Conrad's Roofing &amp; Construction</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Millcreek</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AFRtanAgbrhxQxNHmB1ZTX</t>
+          <t>https://claude.ai/artifact/YQJ3JwkvSt8jQ8gxkA3UgK</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1283,12 +1279,12 @@
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>What is a FORTIFIED roof? A homeowner's guide to the IBHS standard</t>
+          <t>How much snow can a roof hold? Weights, warning signs and safe removal</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rooftek</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\conrad-s-roofing-construction</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -1309,22 +1305,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>jacksonplumbinghvac.com</t>
+          <t>rooftek</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Jackson Family Plumbing &amp; HVAC</t>
+          <t>RoofTek</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Millcreek</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/CPRKjw5jkso5N8x2fxqYxi</t>
+          <t>https://claude.ai/artifact/AFRtanAgbrhxQxNHmB1ZTX</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1350,12 +1346,12 @@
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>How to keep pipes from freezing (and what to do if they do)</t>
+          <t>What is a FORTIFIED roof? A homeowner's guide to the IBHS standard</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\jacksonplumbinghvac.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rooftek</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1366,7 +1362,7 @@
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; The live page is a "Colorado 24/7 Plumbing Call" template with no phone and nothing to recover (archive back to 2024 is the same). Built from the Google listing only: home + contact + 1 new post. Home targets "plumber west jordan" (630 words; no services, hours, licenses or rating invented)</t>
+          <t>NOT A CLIENT YET. Do not contact this business; NO WEBSITE: built from the Google listing only (name, address, phone, category; no services, hours, licenses or rating invented); No domain yet: canonicals use a .example placeholder. Home + contact + 1 new post</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1372,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>dsihvac.com</t>
+          <t>jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Proformance Heating and Air</t>
+          <t>Jackson Family Plumbing &amp; HVAC</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AL6qDWamg184CgbJaLR3Db</t>
+          <t>https://claude.ai/artifact/CPRKjw5jkso5N8x2fxqYxi</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1414,19 +1410,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="J12" s="7" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>How often to change your furnace filter (and what MERV rating to buy)</t>
+          <t>How to keep pipes from freezing (and what to do if they do)</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\dsihvac.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\jacksonplumbinghvac.com</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -1437,7 +1429,7 @@
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; CHECK FIRST: the domain and old site say "DSI HVAC", Google says Proformance (same phone number). Site down, so it was rebuilt from Internet Archive captures (Nov 2025 and Jan 2026): 7 pages at the same Wix URLs + 1 new post. Home targets "hvac company draper". DSI logo not used; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live page is a "Colorado 24/7 Plumbing Call" template with no phone and nothing to recover (archive back to 2024 is the same). Built from the Google listing only: home + contact + 1 new post. Home targets "plumber west jordan" (630 words; no services, hours, licenses or rating invented)</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1439,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>marble-builders.com</t>
+          <t>dsihvac.com</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Marble Builders</t>
+          <t>Proformance Heating and Air</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Q9dcVxd3VWZVsbNmCdKHfv</t>
+          <t>https://claude.ai/artifact/AL6qDWamg184CgbJaLR3Db</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1487,17 +1479,17 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Lead paint and asbestos: what to know before remodeling an older home</t>
+          <t>How often to change your furnace filter (and what MERV rating to buy)</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\marble-builders.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\dsihvac.com</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1508,7 +1500,7 @@
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. Live site suspended, so it was rebuilt from Internet Archive captures (Mar–Sep 2025): 60 pages at the same WordPress URLs + 1 new post. Home targets "general contractor riverton"; Three phone numbers (Google's 801-828-5540 used); copied "Marble Homes" FAQs removed; no project photos archived; 10 unrecoverable pages and the WordPress demo pages kept noindex; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; CHECK FIRST: the domain and old site say "DSI HVAC", Google says Proformance (same phone number). Site down, so it was rebuilt from Internet Archive captures (Nov 2025 and Jan 2026): 7 pages at the same Wix URLs + 1 new post. Home targets "hvac company draper". DSI logo not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -1518,22 +1510,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>prestigetreeandlandscape.com</t>
+          <t>marble-builders.com</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Prestige Tree And Landscape</t>
+          <t>Marble Builders</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/WPVS4xgTgXQWwQDBK3atWJ</t>
+          <t>https://claude.ai/artifact/Q9dcVxd3VWZVsbNmCdKHfv</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1558,17 +1550,17 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>How to mulch around trees (and why mulch volcanoes hurt them)</t>
+          <t>Lead paint and asbestos: what to know before remodeling an older home</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\prestigetreeandlandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\marble-builders.com</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -1579,7 +1571,7 @@
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 35 pages at the same .php URLs (site build writes real .php files) + 1 new post. Blank live home page replaced; home targets "tree service murray"; 1996 vs 1997 certification; WSJ/Disney claims and rating left out. Live backup files kept noindex (should be deleted)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site suspended, so it was rebuilt from Internet Archive captures (Mar–Sep 2025): 60 pages at the same WordPress URLs + 1 new post. Home targets "general contractor riverton"; Three phone numbers (Google's 801-828-5540 used); copied "Marble Homes" FAQs removed; no project photos archived; 10 unrecoverable pages and the WordPress demo pages kept noindex; rating left out</t>
         </is>
       </c>
     </row>
@@ -1589,22 +1581,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>pineapplepropertygroup.com</t>
+          <t>prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Pineapple Property Group</t>
+          <t>Prestige Tree And Landscape</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R6DVER57ftYS7bXc55rs8e</t>
+          <t>https://claude.ai/artifact/WPVS4xgTgXQWwQDBK3atWJ</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1629,17 +1621,17 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Fair housing basics every Salt Lake City landlord should know</t>
+          <t>How to mulch around trees (and why mulch volcanoes hurt them)</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pineapplepropertygroup.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\prestigetreeandlandscape.com</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -1650,7 +1642,7 @@
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site blocks our network: built from Internet Archive captures (2025–2026). 10 pages at the same URLs (2 empty duplicates kept noindex) + 1 new post. Home targets "property management salt lake city", now one H1 (was 5). Their KPI and property-return figures kept and labelled as theirs; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 35 pages at the same .php URLs (site build writes real .php files) + 1 new post. Blank live home page replaced; home targets "tree service murray"; 1996 vs 1997 certification; WSJ/Disney claims and rating left out. Live backup files kept noindex (should be deleted)</t>
         </is>
       </c>
     </row>
@@ -1660,22 +1652,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>whitepineplumbingut.com</t>
+          <t>pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>White Pine Plumbing</t>
+          <t>Pineapple Property Group</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/FXe8rjPexaoeJu8UMYx5Nm</t>
+          <t>https://claude.ai/artifact/R6DVER57ftYS7bXc55rs8e</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1685,7 +1677,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1700,28 +1692,28 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Hard water and your plumbing: what it does and how to check yours</t>
+          <t>Fair housing basics every Salt Lake City landlord should know</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\whitepineplumbingut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pineapplepropertygroup.com</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
+          <t>Applied and checked 23 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (empty /blank/ becomes the blog index) + 1 new post. Home targets "plumber south jordan", now with one H1; Phone is a 435 number: copied exactly. Stock images not used; rating left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site blocks our network: built from Internet Archive captures (2025–2026). 10 pages at the same URLs (2 empty duplicates kept noindex) + 1 new post. Home targets "property management salt lake city", now one H1 (was 5). Their KPI and property-return figures kept and labelled as theirs; rating left out</t>
         </is>
       </c>
     </row>
@@ -1731,22 +1723,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>hvaccowboy.com</t>
+          <t>whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Cowboy Heating &amp; Air</t>
+          <t>White Pine Plumbing</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>South Jordan</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MC4t41ej3hDwZ5cSmFUf2K</t>
+          <t>https://claude.ai/artifact/FXe8rjPexaoeJu8UMYx5Nm</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1769,15 +1761,19 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide and your furnace: what to know before winter</t>
+          <t>Hard water and your plumbing: what it does and how to check yours</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\hvaccowboy.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\whitepineplumbingut.com</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1788,7 +1784,7 @@
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. Live site is a JavaScript app (search engines see 10 words): rebuilt as plain HTML (630 readable words) + 1 new post. Home targets "hvac company lehi"; Live schema says 3 reviews vs 162 on Google: rating left out. Award and Daikin/Bryant claims kept, to confirm</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (empty /blank/ becomes the blog index) + 1 new post. Home targets "plumber south jordan", now with one H1; Phone is a 435 number: copied exactly. Stock images not used; rating left out</t>
         </is>
       </c>
     </row>
@@ -1798,22 +1794,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>anyandallservices.com</t>
+          <t>hvaccowboy.com</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Any &amp; All Services</t>
+          <t>Cowboy Heating &amp; Air</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
+          <t>https://claude.ai/artifact/MC4t41ej3hDwZ5cSmFUf2K</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1836,19 +1832,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="J18" s="7" t="inlineStr"/>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>6 signs you need an electrician, according to NFPA</t>
+          <t>Carbon monoxide and your furnace: what to know before winter</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\hvaccowboy.com</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -1859,7 +1851,7 @@
       <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business. Live site is a JavaScript app (search engines see 10 words): rebuilt as plain HTML (630 readable words) + 1 new post. Home targets "hvac company lehi"; Live schema says 3 reviews vs 162 on Google: rating left out. Award and Daikin/Bryant claims kept, to confirm</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1861,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>sterlingtreeco.godaddysites.com</t>
+          <t>anyandallservices.com</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Sterling Tree Co.</t>
+          <t>Any &amp; All Services</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1884,7 +1876,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
+          <t>https://claude.ai/artifact/XEDjGNAfB6LMNFGr43ZTfv</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1907,15 +1899,19 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Why topping hurts trees (and what arborists do instead)</t>
+          <t>6 signs you need an electrician, according to NFPA</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\anyandallservices.com</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1926,7 +1922,7 @@
       <c r="N19" s="7" t="inlineStr"/>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business; The live site now says they CONNECT homeowners with electricians (referral model): check before pitching. 6 pages at the same URLs + 1 new post. Home targets "electrician salt lake city", honestly framed, one H1; 13 vs 14 years on their own site. Wix template legal pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -1936,22 +1932,22 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>actionyardcare.com</t>
+          <t>sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Action Lawn &amp; Yardcare</t>
+          <t>Sterling Tree Co.</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
+          <t>https://claude.ai/artifact/VneVXfgXqnNncKDiy9ey2e</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1974,30 +1970,26 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="J20" s="7" t="inlineStr"/>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>How high should you mow a Utah lawn?</t>
+          <t>Why topping hurts trees (and what arborists do instead)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\sterlingtreeco.godaddysites.com</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 22 Oct</t>
+          <t>Applied and checked 22 Oct (incl. scrolled header)</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr"/>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 1 page at the same URL (free GoDaddy subdomain) rebuilt as a full home page (137 → 743 words) + 1 new post. Home targets "tree service salt lake city"; Phone is a 315 (New York) number: copied exactly, ask for a local one. Rating left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -2007,22 +1999,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>danielswildlife.com</t>
+          <t>actionyardcare.com</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Daniel's Wildlife &amp; Pest Control</t>
+          <t>Action Lawn &amp; Yardcare</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
+          <t>https://claude.ai/artifact/MJNDgF8Xq98TbyiBSk6fTv</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2047,17 +2039,17 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Found mouse droppings? How to clean up safely</t>
+          <t>How high should you mow a Utah lawn?</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\actionyardcare.com</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -2068,7 +2060,7 @@
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs + 1 new post. Home targets "landscaping murray" (83 → 580 words, incl. a sourced USU yard calendar); Name: Google "Action Lawn and Yard" vs site "Action Lawn &amp; Yardcare"; Site shows no address: Google address used. Rating and "highest rated" claim left out</t>
         </is>
       </c>
     </row>
@@ -2078,22 +2070,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>greenjanitorialservice.com</t>
+          <t>danielswildlife.com</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Green Janitorial Services</t>
+          <t>Daniel's Wildlife &amp; Pest Control</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
+          <t>https://claude.ai/artifact/9UEr9R6FCEHUojmn9ugevz</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2116,15 +2108,19 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Is that cleaner really green? How to read eco labels</t>
+          <t>Found mouse droppings? How to clean up safely</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\danielswildlife.com</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2135,7 +2131,7 @@
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs + 1 new post. Home targets "pest control cottonwood heights", now with one H1; Site shows only "Northern Utah": Google address used, confirm it can be shown. Rating left out until confirmed; generated/stock images left out</t>
         </is>
       </c>
     </row>
@@ -2145,22 +2141,22 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>emetplumbingservices.com</t>
+          <t>greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Emet Plumbing Heating &amp; Air</t>
+          <t>Green Janitorial Services</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
+          <t>https://claude.ai/artifact/Xv6PrRiYmuopb4KKytWdnV</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2183,19 +2179,15 @@
           <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Furnace filters and MERV ratings, explained</t>
+          <t>Is that cleaner really green? How to read eco labels</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\greenjanitorialservice.com</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -2206,7 +2198,7 @@
       <c r="N23" s="7" t="inlineStr"/>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 sitemap URLs + their 6 blog posts at the same URLs, + 1 new post. Home targets "janitorial services south salt lake", now one H1; Live site is stock photos except the vans: supporting photos are credited Commons pictures. Rating and badge left out until confirmed</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2208,22 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>everworklandscape.com</t>
+          <t>emetplumbingservices.com</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Everwork Property Maintenance &amp; Landscaping</t>
+          <t>Emet Plumbing Heating &amp; Air</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
+          <t>https://claude.ai/artifact/26p1PWqb72ktE8PJGLhQoC</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2256,17 +2248,17 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>How to water a Utah lawn: deeper, less often</t>
+          <t>Furnace filters and MERV ratings, explained</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\emetplumbingservices.com</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -2277,7 +2269,7 @@
       <c r="N24" s="7" t="inlineStr"/>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 14 pages at the same URLs + 1 new post (their 5 posts kept). Home targets "plumber taylorsville", now with one H1; Address: Google 5941 S Redwood Rd, Taylorsville (used) vs site 50 Broadway Ste. 300, SLC; Fee conflict: $59.99 diagnostic vs $59.00 service call fee. Badges, unsourced HVAC stats and stock/AI images left out</t>
         </is>
       </c>
     </row>
@@ -2287,22 +2279,22 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>iraut.com</t>
+          <t>everworklandscape.com</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Investment Realty Advisors</t>
+          <t>Everwork Property Maintenance &amp; Landscaping</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
+          <t>https://claude.ai/artifact/9xfg6yFHmov1EZ5M6sYB9r</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2327,17 +2319,17 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>1031 exchange rules: what Utah real estate investors need to know</t>
+          <t>How to water a Utah lawn: deeper, less often</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\everworklandscape.com</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -2348,7 +2340,7 @@
       <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
+          <t>NOT A CLIENT YET. Do not contact this business; Live site was rebuilt after the 21 Oct audit (now 41 pages): smaller win than the report shows. 41 pages at the same URLs + 1 new post. Home targets "landscaping sandy"; Site claims 5.0 on Google; listing shows 4.9 from 210 (claim removed). Only their own job photos used</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2350,22 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>applianceserviceut.com</t>
+          <t>iraut.com</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>ASI Appliance Services</t>
+          <t>Investment Realty Advisors</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
+          <t>https://claude.ai/artifact/Xw6NuY91DcHoymQUkso3yt</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2398,17 +2390,17 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Clothes dryer fire safety: the lint habit that matters most</t>
+          <t>1031 exchange rules: what Utah real estate investors need to know</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\iraut.com</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2419,7 +2411,7 @@
       <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star rating: flag to Angelo before pitching. 48 pages at the same URLs + 1 new post (28 Wix leftovers kept noindex). Home targets "property management midvale"; AUM: $380M vs $400M+ on their own pages</t>
         </is>
       </c>
     </row>
@@ -2429,22 +2421,22 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>triplejlandscaping.com</t>
+          <t>applianceserviceut.com</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Triple J Landscaping</t>
+          <t>ASI Appliance Services</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
+          <t>https://claude.ai/artifact/QuesvqppjbZ8aWDratUStm</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2469,17 +2461,17 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>How much to water your lawn in Utah: the half-inch rule</t>
+          <t>Clothes dryer fire safety: the lint habit that matters most</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\applianceserviceut.com</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2490,7 +2482,7 @@
       <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 5 pages at the same URLs (4 + 1 new post). Home targets "appliance repair salt lake city"; Address: Google 2755 S 300 W (used) vs site 359 W Ironwood Dr; Stock photos not used: credited Commons photos</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2492,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>joestreecareutah.com</t>
+          <t>triplejlandscaping.com</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Joe's Tree Care / Joe's Stump Grinding</t>
+          <t>Triple J Landscaping</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
+          <t>https://claude.ai/artifact/PVYye3ocHYF3gPUEPKS8oP</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2540,17 +2532,17 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>How to water trees in Utah: deep, slow and less often</t>
+          <t>How much to water your lawn in Utah: the half-inch rule</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\triplejlandscaping.com</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2561,7 +2553,7 @@
       <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 8 pages at the same URLs (7 + 1 new post). Home targets "landscaping salt lake city"; Address from their site (none on Google); AI-looking/stock gallery images not used; unverified stats and testimonials left out</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2563,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>utahbluechipcarpetcleaning.com</t>
+          <t>joestreecareutah.com</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Blue Chip Carpet Cleaning</t>
+          <t>Joe's Tree Care / Joe's Stump Grinding</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -2586,7 +2578,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
+          <t>https://claude.ai/artifact/R8BHvZChzoiZB2K7Sb8g92</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2611,17 +2603,17 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
+          <t>How to water trees in Utah: deep, slow and less often</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\joestreecareutah.com</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2632,7 +2624,7 @@
       <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 13 pages at the same URLs (12 + 1 new post). Home targets "tree service salt lake city"; Name: Google "Joe's Stump Grinding" vs site "Joe's Tree Care" (site brand used); Leftover lawn-care template text removed. Their own job photos only</t>
         </is>
       </c>
     </row>
@@ -2642,22 +2634,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>trustyappliancerepairutah.com</t>
+          <t>utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Trusty Appliance Repair</t>
+          <t>Blue Chip Carpet Cleaning</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
+          <t>https://claude.ai/artifact/4JR5cWeF8N3GdeTr2qhkpn</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2682,17 +2674,17 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
+          <t>Wet carpet after a leak: the 24–48 hour rule for stopping mold</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\utahbluechipcarpetcleaning.com</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2703,7 +2695,7 @@
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). Home targets "carpet cleaning salt lake city"; Phone differs: Google 801-785-7385 (used) vs site 801-645-3501; Duct price $10 vs $15 on their pages; Wix stock photos not used</t>
         </is>
       </c>
     </row>
@@ -2713,22 +2705,22 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>vogldirect.com</t>
+          <t>trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Vogl Direct</t>
+          <t>Trusty Appliance Repair</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Eagle Mountain</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
+          <t>https://claude.ai/artifact/8yCD7GBZV5bGbeeUPiG9Hz</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2753,17 +2745,17 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
+          <t>What temperature should your fridge and freezer be? A food-safety guide</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\trustyappliancerepairutah.com</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2774,7 +2766,7 @@
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 12 pages at the same URLs (11 + 1 new post). Home targets "appliance repair sandy"; Address differs: Google says Sandy, the site says Midvale (Google used, flagged); All site photos were stock: credited Commons photos used</t>
         </is>
       </c>
     </row>
@@ -2784,22 +2776,22 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>ahc-utah.com</t>
+          <t>vogldirect.com</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Affordable Heating &amp; Cooling</t>
+          <t>Vogl Direct</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Eagle Mountain</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
+          <t>https://claude.ai/artifact/F2UqCRnjRnPPj2fMzikTFJ</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2824,17 +2816,17 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
+          <t>R-22 and your air conditioner: what Utah homeowners should know</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\vogldirect.com</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2845,7 +2837,7 @@
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 23 pages at the same URLs (22 + 1 new post). Home targets "hvac company salt lake city"; All site photos were Shutterstock: credited Wikimedia Commons photos used instead; No street address (none on Google); Google rating not shown; lorem-ipsum and empty pages kept noindex</t>
         </is>
       </c>
     </row>
@@ -2855,22 +2847,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>mountainwindowcleaning.com</t>
+          <t>ahc-utah.com</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Mountain Window Cleaning</t>
+          <t>Affordable Heating &amp; Cooling</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
+          <t>https://claude.ai/artifact/6d3P7DddpY5d91Zr2kN286</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2880,7 +2872,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -2895,28 +2887,28 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Why birds hit your windows, and how to stop it</t>
+          <t>Carbon monoxide at home: sources, symptoms and where alarms belong</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ahc-utah.com</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Applied and checked 21 Oct</t>
+          <t>Applied and checked 22 Oct</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr"/>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 18 pages at the same URLs (17 + 1 new post), recovered from the Internet Archive because the live site blocks us. Home targets "hvac company salt lake city"; No photos of their own: credited Wikimedia Commons park photos; Google rating and 2024 promotion amounts not shown; AC/furnace repair pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2926,22 +2918,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>rwkconstruction.com</t>
+          <t>mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>RWK Construction Co.</t>
+          <t>Mountain Window Cleaning</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Bluffdale</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
+          <t>https://claude.ai/artifact/93wPKgPqXsWRLEBvxTY1qa</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2966,17 +2958,17 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
+          <t>Why birds hit your windows, and how to stop it</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\mountainwindowcleaning.com</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -2987,7 +2979,7 @@
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post), static .html files on the www host. Home targets "window cleaning sandy"; Stock-looking photos removed; confirm the job photos are theirs; Street address not on their site, so not shown; Google rating not shown; pressure washing, gutters and lights pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -2997,22 +2989,22 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>5starkb.com</t>
+          <t>rwkconstruction.com</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>5 Star Kitchen and Bath</t>
+          <t>RWK Construction Co.</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Bluffdale</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
+          <t>https://claude.ai/artifact/KkkuKUuYVbX7Rkb2hDQgRn</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -3037,17 +3029,17 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
+          <t>Radon in Utah homes: when to test, what the numbers mean, and how it's fixed</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rwkconstruction.com</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -3058,7 +3050,7 @@
       <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 20 pages at the same URLs (19 + 1 new post), six old posts kept. Home targets "general contractor bluffdale"; Most live gallery images are 404; galleries rebuilt from the photos that still load; Unproven claims and the Google rating not shown; kitchen and bathroom pages wait for the client</t>
         </is>
       </c>
     </row>
@@ -3068,27 +3060,27 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>acs-hoa.com</t>
+          <t>5starkb.com</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Advanced Community Services</t>
+          <t>5 Star Kitchen and Bath</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
+          <t>https://claude.ai/artifact/B5unGDmZqbRxDWU4TXcYki</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -3103,22 +3095,22 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>The HOA board's winter checklist for Utah communities</t>
+          <t>Moisture and mold in the bathroom: what to fix, and when to remodel</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\5starkb.com</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -3129,7 +3121,7 @@
       <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 17 pages at the same URLs (16 + 1 new post). The home page targets "bathroom remodeling midvale"; Testimonials page was unedited template text (kept noindex); 10+ years, A+ BBB and the 200-location dealer network left out; stock and manufacturer images removed</t>
         </is>
       </c>
     </row>
@@ -3139,22 +3131,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>equitypmusa.com</t>
+          <t>acs-hoa.com</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Equity Real Estate Property Management</t>
+          <t>Advanced Community Services</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
+          <t>https://claude.ai/artifact/KAioPjYpmrhnLNZ79jMJGD</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3179,17 +3171,17 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>How to spot a rental listing scam before you pay a dime</t>
+          <t>The HOA board's winter checklist for Utah communities</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\acs-hoa.com</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -3200,7 +3192,7 @@
       <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
+          <t>NOT A CLIENT YET. Do not contact this business; 3.2-star Google rating: flag to Angelo before any pitch. 9 pages at the same URLs (8 static .html pages + 1 new post). HOA management leads; Phone: site 1-877-844-4227 vs Google 801-641-1844 (both shown); office list from a 2015-era site needs confirming; all photos were stock</t>
         </is>
       </c>
     </row>
@@ -3210,27 +3202,27 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>abode.cleaning</t>
+          <t>equitypmusa.com</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Abode House Cleaning</t>
+          <t>Equity Real Estate Property Management</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
+          <t>https://claude.ai/artifact/NRPdqgMmE6sWHZ87kakMRh</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link)</t>
+          <t>Anyone with the link</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -3245,22 +3237,22 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (21 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Cleaning products and the air in your home: a plain-language guide</t>
+          <t>How to spot a rental listing scam before you pay a dime</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\equitypmusa.com</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -3271,7 +3263,7 @@
       <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 22 pages at the same URLs (21 + 1 new post). The home page targets "property management sandy"; 13 /properties pages are Wix sample listings (kept noindex; remove live); Stock/AI photos removed; the eviction-rate and renter-pet statistics left out; ask about HOA management</t>
         </is>
       </c>
     </row>
@@ -3281,27 +3273,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>lockthesmithut.com</t>
+          <t>abode.cleaning</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Lockthesmith</t>
+          <t>Abode House Cleaning</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
+          <t>https://claude.ai/artifact/9LN4MJ1hHPtj2CLz6fQyCH</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -3316,22 +3308,22 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Hot cars and locked doors: what every Utah driver should know</t>
+          <t>Cleaning products and the air in your home: a plain-language guide</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\abode.cleaning</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -3342,7 +3334,7 @@
       <c r="N39" s="7" t="inlineStr"/>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "house cleaning draper"; The site shows no phone; Google's number added; Google address lacks the "W" the site's legal pages use; two different service areas on the site; volume claims (20,000+ homes, 400+ teams) left out</t>
         </is>
       </c>
     </row>
@@ -3352,27 +3344,27 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>rasmussenlandscapes.com</t>
+          <t>lockthesmithut.com</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Rasmussen Landscapes</t>
+          <t>Lockthesmith</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
+          <t>https://claude.ai/artifact/Wwa6TdgiQ4DJNMdueHTGUD</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link)</t>
+          <t>Anyone with the link</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -3387,22 +3379,22 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (21 Oct)</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>When should you start watering your lawn in Utah?</t>
+          <t>Hot cars and locked doors: what every Utah driver should know</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\lockthesmithut.com</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -3413,7 +3405,7 @@
       <c r="N40" s="7" t="inlineStr"/>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 11 pages at the same URLs (10 + 1 new post). The home page targets "locksmith west valley city"; Leftover WordPress pages (hello-world, new-site, logo attachments) kept as noindex; remove or redirect them live; No real photos: the old hero was copied from another locksmith's site; the email is on a different domain; the new-customer offer needs confirming</t>
         </is>
       </c>
     </row>
@@ -3423,22 +3415,22 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>ezelectric.com</t>
+          <t>rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>EZ Electric</t>
+          <t>Rasmussen Landscapes</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
+          <t>https://claude.ai/artifact/N7WFyfLzDLFmVtqg2wwF86</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3463,17 +3455,17 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
+          <t>When should you start watering your lawn in Utah?</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\rasmussenlandscapes.com</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -3484,7 +3476,7 @@
       <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 95 pages at the same URLs (94 + 1 new post). The home page targets "landscaping south salt lake"; Address conflict: the site says Salt Lake City, Google says South Salt Lake; Google version shown; "Premier", "best in the business" and "50 years" left out; template filler removed from several thin pages; Universal Analytics tag no longer collects</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3486,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>therepairpros.com</t>
+          <t>ezelectric.com</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>The Repair Pros</t>
+          <t>EZ Electric</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -3509,7 +3501,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
+          <t>https://claude.ai/artifact/7qe4SK8Z1dofTybixafW1U</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3534,17 +3526,17 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Repair or replace? How long appliances actually last</t>
+          <t>Winter electrical safety in Utah: space heaters, holiday lights and extension cords</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\ezelectric.com</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -3555,7 +3547,7 @@
       <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 7 pages at the same URLs (6 + 1 new post). The home page targets "electrician salt lake city"; Two phone numbers: (385) 284-0394 on the site header vs (385) 220-7815 on Google; 284-0394 used; "Over 15 years", "top-rated", "guaranteed" and "certified" left out; a review's "CEO, Acme Industries" template label dropped; stock photos removed</t>
         </is>
       </c>
     </row>
@@ -3565,27 +3557,27 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>pestx.org</t>
+          <t>therepairpros.com</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Pestx</t>
+          <t>The Repair Pros</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
+          <t>https://claude.ai/artifact/8uYtk18z5gPRQHTCCtqhL7</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Anyone with the link</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -3600,22 +3592,22 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
+          <t>Built premium from the start (21 Oct)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
+          <t>Repair or replace? How long appliances actually last</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\therepairpros.com</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3626,7 +3618,7 @@
       <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 4 pages at the same URLs (3 + 1 new post). The home page targets "appliance repair salt lake city"; HTTPS certificate broken: the site only works on http, so http canonicals are kept until it's fixed; "Hundreds of 5-star reviews" and awards left out; brand authorizations kept as stated (confirm); 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -3636,22 +3628,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>foundationrepairogden.com</t>
+          <t>pestx.org</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Fortified Foundations</t>
+          <t>Pestx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
+          <t>https://claude.ai/artifact/Ubx3hF7VSkt6GNL7oNytNr</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3661,7 +3653,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3671,37 +3663,33 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium (21 Oct); v2 full-width photo banner added (21 Oct)</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
+          <t>Ticks in Utah: where they live, when they bite, and what to do</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\Weak-Site-Businesses\pestx.org</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>Fixed and republished 18 Oct</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
-        </is>
-      </c>
+          <t>Applied and checked 21 Oct</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr"/>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
+          <t>NOT A CLIENT YET. Do not contact this business. 19 pages at the same URLs (18 + 1 new post). The home page targets "pest control midvale"; Office address 661 W 7250 S, Midvale comes from Google (no address on the site): confirm; AI-generated photos removed; Google rating not shown; 10 services in the report have no page (ask the client)</t>
         </is>
       </c>
     </row>
@@ -3711,22 +3699,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>rhinofoundationsystems.com</t>
+          <t>foundationrepairogden.com</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Rhino Foundation Systems</t>
+          <t>Fortified Foundations</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>American Fork</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
+          <t>https://claude.ai/artifact/GeENUWMgr1s9NWHQnzvSu8</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3746,22 +3734,22 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
+          <t>Is Your Home Ready for an Earthquake? A Foundation-First Checklist for Ogden Homeowners</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\foundationrepairogden.com</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3771,12 +3759,12 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
+          <t>who owns the site, the current page list, a real logo and address, and proof for the insured/bonded/engineer claims.</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
+          <t>"Check first": no Google profile, and the site runs on a lead-generation template. Confirm who owns it; The live site is behind Cloudflare, so it was rebuilt from Internet Archive captures (home Dec 2024, others Sep 2020): 15 pages at the same URLs; the report counts 23, so some are missing. Unverifiable claims, badge ratings, testimonials and prices left out. All drawn (template images are stock)</t>
         </is>
       </c>
     </row>
@@ -3786,22 +3774,22 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>sandsroofingutah.com</t>
+          <t>rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>S&amp;S Roofing, Inc.</t>
+          <t>Rhino Foundation Systems</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>American Fork</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
+          <t>https://claude.ai/artifact/DuJxZP4scnMpU6TD7FTiG7</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3821,22 +3809,22 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 20 Oct</t>
+          <t>Built premium from the start (20 Oct)</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
+          <t>Radon and Foundation Cracks: What Utah Homeowners Should Know</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\Foundation-Waterproofing-Restoration\rhinofoundationsystems.com</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3846,12 +3834,12 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
+          <t>the current page list or a site export, the main phone and address, and proof for the years/reviews/warranty claims.</t>
         </is>
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
+          <t>The live site is unreachable from our network, so it was rebuilt from Internet Archive captures (Jul-Sep 2025): 35 pages at the same URLs. The report counts 96 pages now, so newer pages are missing. The home page targets "foundation repair american fork"; Phone: site 801-509-5344 vs Google 435-660-5182; no address on the site; 40+ years, warranties, review counts and case studies left out. Only their own photos (stock removed)</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3849,22 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>stgeorgeconcreteleveling.com</t>
+          <t>sandsroofingutah.com</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>St. George Concrete Leveling</t>
+          <t>S&amp;S Roofing, Inc.</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
+          <t>https://claude.ai/artifact/D8f3gfxdw39eASzkY6G16x</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3896,22 +3884,22 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (20 Oct 2026)</t>
+          <t>Premium redesign (v2) published 20 Oct</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
+          <t>How Much Snow Can Your Roof Hold? A Utah Homeowner's Guide</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sandsroofingutah.com</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -3921,12 +3909,12 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
+          <t>which address to show, OK to show the review numbers, whether they do installation/leak/emergency/inspection/flat roof repair as separate services, and that the 16 ad landing pages may be noindex.</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
+          <t>Address: the site says Salt Lake City, Google says West Valley City (same street and ZIP); 4.6 stars / 149 reviews not shown until confirmed; Unverified claims left out. Tracking kept as live (Google Ads, Amazon pixel, GTM)</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3924,12 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>m3industriesconcrete.com</t>
+          <t>stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>M3 Industries</t>
+          <t>St. George Concrete Leveling</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -3951,7 +3939,7 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
+          <t>https://claude.ai/artifact/9vxQFwaudXcFQfFto3uACz</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3976,17 +3964,17 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
+          <t>Is Your Sprinkler System Sinking Your Concrete? Finding Irrigation Leaks Before They Wash Out a Slab</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgeconcreteleveling.com</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -3996,12 +3984,12 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
+          <t>who owns the site, proof for the years/customers/certification/warranty claims, real job photos, and whether they do foundation repair.</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
+          <t>"Check first", no Google profile, reads like a lead-generation site: confirm ownership; Unverified claims and page anecdotes left out; No real photos (the only one was stock): drawn</t>
         </is>
       </c>
     </row>
@@ -4011,22 +3999,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>thedisasterrepairteam.com</t>
+          <t>m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Disaster Repair Team</t>
+          <t>M3 Industries</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
+          <t>https://claude.ai/artifact/EBFsPoMHNf28A9zR4gvgcn</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -4051,17 +4039,17 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
+          <t>Cutting or Grinding Concrete Yourself? Read This About Silica Dust First</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\m3industriesconcrete.com</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4071,12 +4059,12 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
+          <t>20+ vs 25+ years, a Google Business Profile, whether Merrill is the owner, more real photos (coatings, stamped), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
+          <t>"Check first" and no Google profile; The live contact page is the Wix template (San Francisco placeholder): replaced with the client's real details; Many live images look AI-generated (not used)</t>
         </is>
       </c>
     </row>
@@ -4086,22 +4074,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>poly-lift.com</t>
+          <t>thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Poly-Lift</t>
+          <t>Disaster Repair Team</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
+          <t>https://claude.ai/artifact/VPW5ZqTJiGGSLd3SsQPvvd</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -4126,17 +4114,17 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
+          <t>Frozen Pipes in a Utah Winter: Prevent Them, Thaw Them, and What to Do When One Bursts</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\thedisasterrepairteam.com</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -4146,12 +4134,12 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
+          <t>which phone and address to use everywhere, real job photos to replace the AI images, whether the truck photo is real, and water damage keyword data from Angelo.</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
+          <t>"Check first" on the outreach list; Most live images are AI-generated (not used; only the real job photos are); Phone and address differ from Google</t>
         </is>
       </c>
     </row>
@@ -4161,22 +4149,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>stgeorgehomeservices.com</t>
+          <t>poly-lift.com</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>St. George Home Services</t>
+          <t>Poly-Lift</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
+          <t>https://claude.ai/artifact/GsXzFR6XAfxgYf7nXT5etB</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -4201,17 +4189,17 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
+          <t>When Is an Uneven Sidewalk a Trip Hazard? The Quarter-Inch Rule, Explained</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\poly-lift.com</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4221,12 +4209,12 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
+          <t>which address is right, OK to show the Google rating (4.6 from 14), whether they do basement waterproofing, and the "check first" warning before outreach.</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
+          <t>"Check first" on the outreach list; Two different addresses on their own site (715 W 1725 N vs 715 N 1725 W)</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4224,12 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>cleartopsolutions.shop</t>
+          <t>stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>ClearTop Solutions</t>
+          <t>St. George Home Services</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -4251,7 +4239,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
+          <t>https://claude.ai/artifact/P1o9fVxviTBh8xkm2oiBTG</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -4276,17 +4264,17 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
+          <t>What Temperature Should Your Water Heater Be? 120, 140, and the Trade-Off</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\stgeorgehomeservices.com</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4296,12 +4284,12 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
+          <t>the home keyword (plumbing vs AC repair), whether to show the license number, the generated-image question, and whether the /win giveaway is still running at go-live.</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
+          <t>Probably the wrong report group (plumber/HVAC, not foundation): the foundation parts of the report weren't applied</t>
         </is>
       </c>
     </row>
@@ -4311,22 +4299,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>jsprofinish.com</t>
+          <t>cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>JS ProFinish</t>
+          <t>ClearTop Solutions</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Clearfield</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
+          <t>https://claude.ai/artifact/NADbV713PdvdM3kfsEJP58</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -4351,17 +4339,17 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
+          <t>Summer Storm Season in St. George: How to Get Your Home Ready for Monsoon Water</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\cleartopsolutions.shop</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -4371,12 +4359,12 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
+          <t>which phone is the main one, proof for the satisfaction/projects/certification claims, real job photos, and an OK to make the home page self-canonical.</t>
         </is>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
+          <t>The site's only photo looks AI-generated (not used): services are drawn, landscapes are openly licensed and credited; Template claims (98%, 100+, five stars, "certified") left out; phone differs from Google; the live home page canonicalises to /st-george/</t>
         </is>
       </c>
     </row>
@@ -4386,22 +4374,22 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>armour-crete.com</t>
+          <t>jsprofinish.com</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Armour Crete</t>
+          <t>JS ProFinish</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>St. George</t>
+          <t>Clearfield</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
+          <t>https://claude.ai/artifact/NFyYZywnJrizCNCTnnb6ut</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -4426,17 +4414,17 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
+          <t>Basement Bedroom Egress Windows in Utah: The Code in Plain English</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jsprofinish.com</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -4446,12 +4434,12 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
+          <t>Angelo to confirm this is the right site for the report's business, OK on the rating text (4.8 from 18, Sept 2026), Pablo as the blog author, and whether they do French drains, foundation or water damage work.</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
+          <t>The report's Google profile is a different business ("Vista Concrete Construction", Ogden): the draft uses only the site's own JS ProFinish facts</t>
         </is>
       </c>
     </row>
@@ -4461,22 +4449,22 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>swiftrestoreutah.com</t>
+          <t>armour-crete.com</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Swift Restoration and Remodeling</t>
+          <t>Armour Crete</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Ogden</t>
+          <t>St. George</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
+          <t>https://claude.ai/artifact/9geFv8ryaJjiV1qnNLr7eR</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -4499,15 +4487,19 @@
           <t>Built premium from the start (20 Oct 2026)</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
+          <t>White Stains on Concrete in St. George: What Efflorescence Is and How to Stop It</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\armour-crete.com</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4517,12 +4509,12 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
+          <t>which business name and main phone to use, their own job photos, OK to show the Google rating (5.0 from 3), and whether they do concrete lifting.</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
+          <t>The site has no photos: services are drawn, landscapes are openly licensed and credited; Name and phone mismatches (Armour Crete vs Armored Concrete Systems; three phones)</t>
         </is>
       </c>
     </row>
@@ -4532,22 +4524,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>exceptional-roofing.com</t>
+          <t>swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Exceptional Roofing</t>
+          <t>Swift Restoration and Remodeling</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Ogden</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
+          <t>https://claude.ai/artifact/B2QshwWSgPtaXdMw6U4XXJ</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -4557,7 +4549,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4567,22 +4559,18 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (19 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>Built premium from the start (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr"/>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
+          <t>A Home Fire Safety Checklist for Northern Utah Winters</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\swiftrestoreutah.com</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4592,12 +4580,12 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
+          <t>the right phone ((385) 412-8633 vs 402-8536), OK to show the Google rating (4.6 from 179), confirmation of BBB and IICRC, whether the free-gift pages stay, and more finished-job photos.</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
+          <t>Two phone numbers on the live site; 16 internal links redirect and 2 are 404 (fixed in the draft); the local-guide pages have factual errors (flagged)</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4595,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>sfrutah.com</t>
+          <t>exceptional-roofing.com</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Superior Foundation Repair Utah</t>
+          <t>Exceptional Roofing</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City &amp; St. George</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
+          <t>https://claude.ai/artifact/DEZfmiUd1wYyZcNVpxwzNE</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -4647,17 +4635,17 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
+          <t>Ice Dams on Utah Roofs: Why They Form and How to Stop Them</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\exceptional-roofing.com</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4667,12 +4655,12 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
+          <t>which phone leads (estimator vs production), OK to show the Google rating (4.8 from 16), OK to name the Leonardo Museum project, whether they want a roof installation page, and more photos with towns.</t>
         </is>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
+          <t>Live internal links point to a broken /wb_exceptional-roofing.com/ path; WordPress leftovers (hello-world, sample-page) need redirects. No address shown (service-area business)</t>
         </is>
       </c>
     </row>
@@ -4682,22 +4670,22 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>dryhouse.com</t>
+          <t>sfrutah.com</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Rocky Mountain Waterproofing</t>
+          <t>Superior Foundation Repair Utah</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>West Jordan</t>
+          <t>Salt Lake City &amp; St. George</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
+          <t>https://claude.ai/artifact/86QxxTHxLtXaue75TF51sX</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4720,15 +4708,19 @@
           <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
+          <t>Expansive Clay in St. George: Why Southern Utah Foundations Crack</t>
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\sfrutah.com</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -4738,12 +4730,12 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
+          <t>whether the live rebuild is intentional, the correct office addresses and phones (and what the Midvale address is), the years-in-business claim (founded 2019 vs "15+ years"), OK to show the Google rating (5.0 from 17), the 7 missing blog posts, and more job photos.</t>
         </is>
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
+          <t>The live site is broken today (the home page is a template 404), so the content was rebuilt from Wayback captures (Mar–Jul 2026); The addresses and phone labels conflict on the old site; 7 newer blog posts have no archive copy</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4745,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>davenportfoundationrepair.com</t>
+          <t>dryhouse.com</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Davenport Foundation Repair</t>
+          <t>Rocky Mountain Waterproofing</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -4768,7 +4760,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
+          <t>https://claude.ai/artifact/82L9VDK7QfiqSmg9mERV6P</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -4791,19 +4783,15 @@
           <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
+      <c r="J59" s="7" t="inlineStr"/>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
+          <t>Before You Backfill: A Foundation Checklist for Utah Builders</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\dryhouse.com</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -4813,12 +4801,12 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
+          <t>confirmation that the domain stays dryhouse.com, OK to show the Google rating (4.8 from 50), whether they're still a licensed pesticide company, product copy for TremProof 250 GC and the horizontal services, current owners and team, more job photos with cities, and a GA4 setup.</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
+          <t>Several live pages were template filler (lorem ipsum, menu demo, "Description of..."); they are rebuilt from the client's own text; The analytics tag is a defunct UA ID</t>
         </is>
       </c>
     </row>
@@ -4828,22 +4816,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>saltcityroofers.com</t>
+          <t>davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Salt City Roofers</t>
+          <t>Davenport Foundation Repair</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>West Jordan</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
+          <t>https://claude.ai/artifact/HDmbp95dF7QLxG8RbfYg91</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4853,7 +4841,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>18 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -4863,22 +4851,22 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (19 Oct 2026)</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>514</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
+          <t>Collapsible Soils in Utah: Why Some Homes Settle When the Ground Gets Wet</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\davenportfoundationrepair.com</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -4888,12 +4876,12 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
+          <t>the main phone number (1-801-569-2302 or 1-801-429-9989), OK to show the Google rating, whether the 2017 awards and team list are current, more of their own job photos at full size, and how to handle the CMS item pages (keep or redirect).</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
+          <t>Their big product photos are Basement Systems / Supportworks network images, so none are used; Deeper CMS item pages (single reviews, photos, before/after items) are not rebuilt; Angelo needs the redirect CSV</t>
         </is>
       </c>
     </row>
@@ -4903,22 +4891,22 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>utahroofingpros.com</t>
+          <t>saltcityroofers.com</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Utah Roofing Pros</t>
+          <t>Salt City Roofers</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Cottonwood Heights</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
+          <t>https://claude.ai/artifact/2GHetZh1KXWob6jRhfRr8g</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -4938,22 +4926,22 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
+          <t>Tear-Off or Roof-Over? Utah's Two-Layer Rule for Re-Roofing</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\saltcityroofers.com</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -4963,12 +4951,12 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
+          <t>whether they're still operating, the phone and address to show, current certifications, which report services they offer (roof repair, metal, gutters, inspections, commercial), and a high-resolution logo.</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>The current city pages use AI-generated photos; none are used</t>
+          <t>No Google profile found and the last post is from 2022: confirm the business is active. 21 WordPress archive pages need redirects</t>
         </is>
       </c>
     </row>
@@ -4978,22 +4966,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>xperienceroofing.com</t>
+          <t>utahroofingpros.com</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Xperience Roofing</t>
+          <t>Utah Roofing Pros</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Cottonwood Heights</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
+          <t>https://claude.ai/artifact/72r9xBAF2qYrV5hwbzpwcG</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -5013,18 +5001,22 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 21 Oct</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Attic Ventilation for Utah Homes: Intake, Exhaust and Ice Dams</t>
+        </is>
+      </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahroofingpros.com</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -5034,12 +5026,12 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
+          <t>proof of GAF Certified / Owens Corning Preferred, warranty lengths, current financing terms, OK to show 4.9 stars / 104 reviews, whether they do roof leak repair, and OK to name the Saint Ann's School job.</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
+          <t>The current city pages use AI-generated photos; none are used</t>
         </is>
       </c>
     </row>
@@ -5049,22 +5041,22 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>utahoneroofing.com</t>
+          <t>xperienceroofing.com</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Utah One Roofing / One Roofing LLC</t>
+          <t>Xperience Roofing</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
+          <t>https://claude.ai/artifact/SLRVgrNZDzsznmtq8Ajgb3</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -5084,22 +5076,18 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct 2026)</t>
+          <t>Premium redesign (v2) published 21 Oct</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\xperienceroofing.com</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -5109,12 +5097,12 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
+          <t>real job photos with cities, OK to show 4.9 stars / 365 reviews, the product lines behind each system (for lifespans and warranties), and whether they do leak repair, emergency repair, installation and gutters.</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
+          <t>Every photo on the current site is stock captioned as local jobs ("Standing seam metal — Draper, UT"), so the draft uses none; ask for real photos. New journal post: "How to Read a Roofing Estimate: The Line Items That Matter" (1,080 words)</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5112,12 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>roofrepairsaltlakecity.com</t>
+          <t>utahoneroofing.com</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Roof Repair Salt Lake City</t>
+          <t>Utah One Roofing / One Roofing LLC</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -5139,7 +5127,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
+          <t>https://claude.ai/artifact/7qT5pXNwg7ScpXNbLgZ5jW</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -5164,13 +5152,17 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Green Roofs in Utah: How They Work, What They Weigh, and Whether They Fit Our Climate</t>
+        </is>
+      </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\utahoneroofing.com</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -5180,12 +5172,12 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
+          <t>which address is right, "disabled veteran-owned" wording, 24/7 response, years in business and license, financing terms, OK to show 5 stars / 14 reviews, pages for installation / replacement / inspection, 301s or 410s for the demo posts, and a form handler.</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
+          <t>"Check first" on the outreach list; the site and Google profile show different street numbers (5546 vs 5536 W Heathrow Cir)</t>
         </is>
       </c>
     </row>
@@ -5195,22 +5187,22 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>skybridgeroofings.com</t>
+          <t>roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Sky Bridge Roofing</t>
+          <t>Roof Repair Salt Lake City</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>South Salt Lake</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
+          <t>https://claude.ai/artifact/Eo3rxCp5tG94AzRHFCp9Y6</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -5230,22 +5222,18 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (18 Oct)</t>
+          <t>Built premium from the start (18 Oct 2026)</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofrepairsaltlakecity.com</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -5255,12 +5243,12 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+          <t>which phone and address are right, real job photos, whether 24/7 service is real, current manufacturer certifications, merging the near-duplicate commercial and TPO pages (Angelo), 301s for the theme demo pages, and a form handler.</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
+          <t>"Check first" on the outreach list; the phone on the site ((385) 355-4849) differs from the Google profile. New article: "What Is a Ballasted Roof? How Stone-Ballasted Single-Ply Roofs Work" (1,040 words)</t>
         </is>
       </c>
     </row>
@@ -5270,22 +5258,22 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>oakleyroofingslc.com</t>
+          <t>skybridgeroofings.com</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Oakley Roofing</t>
+          <t>Sky Bridge Roofing</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>South Salt Lake</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
+          <t>https://claude.ai/artifact/Led1nknLvy4VLCJcy7UNTa</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -5295,7 +5283,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>17 Oct 2026</t>
+          <t>18 Oct 2026</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -5305,7 +5293,7 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Built premium from the start (17 Oct)</t>
+          <t>Built premium from the start (18 Oct)</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
@@ -5315,12 +5303,12 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
+          <t>Do You Need a Permit to Replace a Roof in South Salt Lake?</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\skybridgeroofings.com</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -5328,10 +5316,14 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>OK to show the Google address and 5 stars / 25 reviews, the phone format, which email domain is right, real reviews, which warranty and speed claims are true, years in business and licenses, roof installation / storm damage / insurance claims, more job photos with cities, a form handler, and 301s for the two Shopify leftovers.</t>
+        </is>
+      </c>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
+          <t>The report marks this business "Check first" on the outreach list; the email on their site uses skybridgeroofing.com (no "s")</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5333,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>mandmgutters.com</t>
+          <t>oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>M&amp;M Gutters &amp; Exteriors</t>
+          <t>Oakley Roofing</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -5356,7 +5348,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
+          <t>https://claude.ai/artifact/JQP1taU8wLYD3KqMn8qEEQ</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -5376,22 +5368,22 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 17 Oct</t>
+          <t>Built premium from the start (17 Oct)</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
+          <t>TPO vs. EPDM vs. PVC: Which Flat Roof Membrane Fits Your Building?</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\oakleyroofingslc.com</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -5399,14 +5391,10 @@
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
-        </is>
-      </c>
+      <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
+          <t>The solar pages list two other phone numbers and an email with a typo; the service area contradicts itself; the partner logos need confirming</t>
         </is>
       </c>
     </row>
@@ -5416,12 +5404,12 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>roofwiseut.com</t>
+          <t>mandmgutters.com</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>RoofWise</t>
+          <t>M&amp;M Gutters &amp; Exteriors</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -5431,7 +5419,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
+          <t>https://claude.ai/artifact/RQhjKtWFoAxx1YDTX7Thx3</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -5456,17 +5444,17 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>What Does Hail Damage Look Like on a Roof?</t>
+          <t>5-Inch vs. 6-Inch Gutters: Which Size Does Your Home Need?</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\mandmgutters.com</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -5476,12 +5464,12 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
+          <t>the review count (413 on the site vs. 427 on Google); whether they do roof repair and metal roofing; what to do with the "Leaf Guard" posts (Angelo); whether the financing rates and badges are current; removing the retired Universal Analytics tags; form handlers</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
+          <t>5 posts target the competitor brand "Leaf Guard" and need a review by Angelo</t>
         </is>
       </c>
     </row>
@@ -5491,22 +5479,22 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>jordanriverroofing.com</t>
+          <t>roofwiseut.com</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Jordan River Roofing</t>
+          <t>RoofWise</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Taylorsville</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
+          <t>https://claude.ai/artifact/QpHuaxtZu8V2suih5SgMga</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -5531,17 +5519,17 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
+          <t>What Does Hail Damage Look Like on a Roof?</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofwiseut.com</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -5551,12 +5539,12 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
+          <t>taking down or redirecting the lovable.app copy; OK to show the street address and 5 stars from 25 reviews; whether they install metal roofs; confirming the stats (200+ customers, 9+ years); real job photos; the brand spelling (RoofWise or Roof-Wise); form handlers</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
+          <t>**The old robots.txt and sitemap point Google to `roofwise-clear-path.lovable.app`**, a duplicate copy of the site; the new ones use roofwiseut.com, with absolute canonicals. Salt Lake City is in the home page and all the service pages. 12 of the 14 images looked AI-made, so the photos are now frames from their own drone video of a real re-roof</t>
         </is>
       </c>
     </row>
@@ -5566,22 +5554,22 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>jemzaroofing.com</t>
+          <t>jordanriverroofing.com</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Jemza Roofing</t>
+          <t>Jordan River Roofing</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Taylorsville</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
+          <t>https://claude.ai/artifact/RvMQbJvcrYJSygqmrPVPfc</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -5601,22 +5589,22 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Premium redesign (v2) published 18 Oct</t>
+          <t>Premium redesign (v2) published 17 Oct</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
+          <t>Ridge Vent vs. Turtle Vents: Which Is Better?</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jordanriverroofing.com</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -5626,12 +5614,12 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
+          <t>the founding year; whether 24/7 emergency service is real; BBB and manufacturer certifications (and the TAMKO tier); OK to show 4.8 stars from 48 reviews; office hours; more real photos; what to do with the 65 service × city pages (Angelo); a form handler</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
+          <t>**The old site is a React app** that shows Google one page: every URL has the same title and meta, and `canonical="/"`. The new site gives every page its own; **65 service × city pages are doorway pages**: they're kept with a canonical to the main service page, and Angelo decides whether to redirect them. Taylorsville is in the home page and all 5 service pages. Only the 7 clearly real photos are used; 24 AI-looking images were dropped. Contradictory numbers (founded 2019 vs. "since 2003", 4.9 vs. 4.8 stars, 24/7, BBB) are left out</t>
         </is>
       </c>
     </row>
@@ -5641,22 +5629,22 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>jandnroofing.com</t>
+          <t>jemzaroofing.com</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>J &amp; N Roofing Maintenance, LLC</t>
+          <t>Jemza Roofing</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>West Valley City</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
+          <t>https://claude.ai/artifact/J5KbkX6Xf8gKYtvacKPjJZ</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -5681,17 +5669,17 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>How Far Should Shingles Overhang the Drip Edge?</t>
+          <t>Chimney Cap vs. Chimney Shroud: What's the Difference?</t>
         </is>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jemzaroofing.com</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -5701,12 +5689,12 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+          <t>whether the testimonials-page reviews are real; OK to show 4.9 stars from 29 reviews; whether they do roof repair and inspections (the biggest keywords); the phone number format; real prices; re-adding the contact form's PHP captcha at go-live</t>
         </is>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+          <t>**The live Testimonials page shows template or fake reviews** (a "tire service" intro, "Jemza Roofing Corp.", 4.5 from 2 reviews); the draft uses only the 4 real reviews from the home page</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5704,12 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>gprroofing.com</t>
+          <t>jandnroofing.com</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Go Pro Roofing</t>
+          <t>J &amp; N Roofing Maintenance, LLC</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -5731,7 +5719,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
+          <t>https://claude.ai/artifact/7ueiGCWmq7oKU9t9UXVSD6</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -5756,17 +5744,17 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>How Are Valleys Done on a Metal Roof?</t>
+          <t>How Far Should Shingles Overhang the Drip Edge?</t>
         </is>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\jandnroofing.com</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -5776,10 +5764,14 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
-        </is>
-      </c>
-      <c r="O72" s="7" t="inlineStr"/>
+          <t>what to do with the copied posts (Angelo), years in business, OK to show references' phone numbers and the street address, whether the special offers are current, real job photos, merging the near-duplicate "roofing salt lake city" posts, and connecting the forms.</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>**411 of the 452 blog posts are copied from goodshomedesign.com** (crafts and cabins, with another site's Amazon affiliate tag); they're left out, and the list is in OUTBOX for Angelo to decide on (410 or noindex). West Valley City is now in the home page and all service page titles and H1s. Private phone numbers are hidden on the References page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -5787,22 +5779,22 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>pioneerroofingutah.com</t>
+          <t>gprroofing.com</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Pioneer Roofing Co</t>
+          <t>Go Pro Roofing</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, est. 1980</t>
+          <t>West Valley City</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
+          <t>https://claude.ai/artifact/KYE28WnNTT3JBVTK4sisRT</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -5827,17 +5819,17 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
+          <t>How Are Valleys Done on a Metal Roof?</t>
         </is>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\gprroofing.com</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -5847,7 +5839,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
+          <t>confirming the FAQ prices and "24/7" claim, GAF Master Elite vs certified, OK to show 5.0 / 62 reviews and the street address, privacy and terms text, merging the two roof-leak posts (Angelo), more real job photos, and connecting the forms.</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr"/>
@@ -5858,22 +5850,22 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>ezroofingnow.com</t>
+          <t>pioneerroofingutah.com</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>EZ Roofing</t>
+          <t>Pioneer Roofing Co</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT &amp; Cabot, AR</t>
+          <t>Salt Lake City, est. 1980</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
+          <t>https://claude.ai/artifact/2DBph6Hboi5WFbs6JKBYsy</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -5898,17 +5890,17 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>The Best Time of Year to Replace a Roof in Utah</t>
+          <t>What Is the 25% Rule for Roofing? (And Does It Apply in Utah?)</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\pioneerroofingutah.com</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -5918,7 +5910,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
+          <t>years in business ("since 1980"?), which warranty wording is current, the TPO price description, OK to show 4.8 stars / 175 reviews, the owner photo caption, merging the two commercial pages (Angelo), and connecting the forms.</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr"/>
@@ -5929,22 +5921,22 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>customroofs.biz</t>
+          <t>ezroofingnow.com</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Custom Roofing LLC</t>
+          <t>EZ Roofing</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Lehi</t>
+          <t>Salt Lake City, UT &amp; Cabot, AR</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
+          <t>https://claude.ai/artifact/KXtcRUpw9gJzLBLsz6gDUz</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5969,17 +5961,17 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>253</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Why Does Copper Turn Green?</t>
+          <t>The Best Time of Year to Replace a Roof in Utah</t>
         </is>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\ezroofingnow.com</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -5989,7 +5981,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
+          <t>merging the two commercial pages and the Salt Lake City city page (Angelo), the 888 vs local phone number, showing 4.7 stars instead of "5 star", local content for the 37 template city pages, the old address on the $25 promo page, and connecting the forms.</t>
         </is>
       </c>
       <c r="O75" s="7" t="inlineStr"/>
@@ -6000,22 +5992,22 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>aluminumlockroofing.com</t>
+          <t>customroofs.biz</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Aluminum Lock Roofing</t>
+          <t>Custom Roofing LLC</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Lehi</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
+          <t>https://claude.ai/artifact/85V1WSqaBzagcJZNHM3aRJ</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -6045,12 +6037,12 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Can You Put a New Roof Over an Old Roof?</t>
+          <t>Why Does Copper Turn Green?</t>
         </is>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\customroofs.biz</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -6060,7 +6052,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
+          <t>⚠ the address (shared with Aluminum Lock Roofing on Google; left off the draft), years in business (75 / 15+ / 20+ conflict), confirming 700+ projects, 1000+ clients, the 5-year warranty and 24/7 repairs, which other services they offer, and connecting the forms.</t>
         </is>
       </c>
       <c r="O76" s="7" t="inlineStr"/>
@@ -6071,22 +6063,22 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>aestheticroofing.com</t>
+          <t>aluminumlockroofing.com</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Aesthetic Roofing</t>
+          <t>Aluminum Lock Roofing</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>South Jordan</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
+          <t>https://claude.ai/artifact/EXdk9gqQYrZJKwQuW9qhqB</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -6096,7 +6088,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>17 Oct 2026</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -6111,17 +6103,17 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>What Causes Roof Leaks?</t>
+          <t>Can You Put a New Roof Over an Old Roof?</t>
         </is>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aluminumlockroofing.com</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -6131,7 +6123,7 @@
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
+          <t>⚠ the address (Google profile shares it with Custom Roofing LLC; left off the draft for now), which services they offer, privacy policy text, blog author, forms need connecting.</t>
         </is>
       </c>
       <c r="O77" s="7" t="inlineStr"/>
@@ -6142,18 +6134,22 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>amcoroof.com</t>
+          <t>aestheticroofing.com</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>American Roofing Company</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr"/>
+          <t>Aesthetic Roofing</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>South Jordan</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+          <t>https://claude.ai/artifact/RCE5PtH3HeJduNU9W3KNtN</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -6178,17 +6174,17 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>How to Prevent Ice Dams on a Utah Roof</t>
+          <t>What Causes Roof Leaks?</t>
         </is>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\aestheticroofing.com</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -6198,7 +6194,7 @@
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+          <t>which phone number is the main one (3 different numbers found), OK to show 4.8 / 350+ reviews, blog author, merge the two gutter pages, forms need connecting, `/sample-page/` should redirect.</t>
         </is>
       </c>
       <c r="O78" s="7" t="inlineStr"/>
@@ -6209,69 +6205,136 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>roofamc.com</t>
+          <t>amcoroof.com</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Advanced Roofing &amp; Moisture Control</t>
+          <t>American Roofing Company</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
+          <t>https://claude.ai/artifact/JLj5SWFKyr3S5HXvR4rohf</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Anyone with the link</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Premium redesign (v2) published 18 Oct</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>How to Prevent Ice Dams on a Utah Roof</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\amcoroof.com</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>Fixed and republished 18 Oct</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>blog author name, OK to rewrite long titles, forms need connecting, 9 redirects to keep.</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>roofamc.com</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Advanced Roofing &amp; Moisture Control</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
           <t>https://claude.ai/artifact/KtP6sjWjk6Nv9zaKZ4oPkH</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>Anyone with the link</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>Premium redesign (v2) published 18 Oct</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="J80" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>How Long Do Roofs Last in Utah?</t>
         </is>
       </c>
-      <c r="L79" s="8" t="inlineStr">
+      <c r="L80" s="8" t="inlineStr">
         <is>
           <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\roofamc.com</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>Fixed and republished 18 Oct</t>
         </is>
       </c>
-      <c r="N79" s="7" t="inlineStr">
+      <c r="N80" s="7" t="inlineStr">
         <is>
           <t>phone and address format, blog author, "4th-generation" claim, forms need connecting.</t>
         </is>
       </c>
-      <c r="O79" s="7" t="inlineStr"/>
+      <c r="O80" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O79"/>
+  <autoFilter ref="A1:O80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -6429,6 +6492,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6527,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6804,17 +6869,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
+          <t>Earthen Phoenix full 17-page site (newest; see Website redesigns above)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
+          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
+          <t>30 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6824,17 +6889,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (older)</t>
+          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
+          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026</t>
+          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
         </is>
       </c>
     </row>
@@ -6844,17 +6909,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix redesign (older)</t>
+          <t>Earthen Phoenix (older)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
+          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>14 Oct 2026</t>
+          <t>15 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6929,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning redesign preview</t>
+          <t>Earthen Phoenix redesign (older)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
+          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -6884,12 +6949,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning site preview (older)</t>
+          <t>Alpine Cleaning redesign preview</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
+          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -6904,12 +6969,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning preview (older)</t>
+          <t>Alpine Cleaning site preview (older)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
+          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -6924,12 +6989,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+          <t>Alpine Cleaning preview (older)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -6944,22 +7009,42 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>14 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
           <t>The 5-Layer Page Infographic</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/JfTPtc3pR4ATt1989Qziph</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -6981,6 +7066,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -721,12 +721,12 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
+          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x (NEWEST: "Ember", original design)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Private until shared (open the link, Share, Anyone with the link). The older home-page link (Jsn9NFxJmciVtundmDbW7H) is public and was not changed.</t>
+          <t>Private until shared (open the link, Share, Anyone with the link)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Full 17-page site with per-service animations (30 Oct)</t>
+          <t>Original Ember design, 17 pages, ember service animations (30 Oct)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="7" t="inlineStr"/>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\earthenphoenix.com\2026-10-30_earthenphoenix.com_full-site-preview</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\earthenphoenix.com\2026-10-30_earthenphoenix.com_ember-site-preview</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Checked 30 Oct (menu panel under header, header pinned after scroll, scrolled header colours)</t>
+          <t>Checked 30 Oct (capsule header stays at top, full-screen menu below it, page locks, links work)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -6592,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix full 17-page site (newest; see Website redesigns above)</t>
+          <t>Earthen Phoenix "Ember" original design (newest; see Website redesigns above)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
+          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
+          <t>Earthen Phoenix full site extending the earlier home design (superseded)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
+          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
+          <t>30 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (older)</t>
+          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
+          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026</t>
+          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
         </is>
       </c>
     </row>
@@ -6929,17 +6929,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix redesign (older)</t>
+          <t>Earthen Phoenix (older)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
+          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>14 Oct 2026</t>
+          <t>15 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning redesign preview</t>
+          <t>Earthen Phoenix redesign (older)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
+          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning site preview (older)</t>
+          <t>Alpine Cleaning redesign preview</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
+          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning preview (older)</t>
+          <t>Alpine Cleaning site preview (older)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
+          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+          <t>Alpine Cleaning preview (older)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -7029,22 +7029,42 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
+          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>14 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
           <t>The 5-Layer Page Infographic</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/JfTPtc3pR4ATt1989Qziph</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D22"/>
+  <autoFilter ref="A1:D23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -7067,6 +7087,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x (NEWEST: "Ember", original design)</t>
+          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Original Ember design, 17 pages, ember service animations (30 Oct)</t>
+          <t>Original Ember design, 17 pages, ember service animations + extra motion layer (30 Oct)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>

--- a/Client-Website-Tracker.xlsx
+++ b/Client-Website-Tracker.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redesigns'!$A$1:$O$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reports only'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Older previews'!$A$1:$D$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -711,7 +711,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix</t>
+          <t>Earthen Phoenix, "The Earthen Atlas", newest</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x</t>
+          <t>https://claude.ai/artifact/9Wp2ERpwNbSbJ5LZ7hxGiP</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>30 Oct 2026</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -741,24 +741,28 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Original Ember design, 17 pages, ember service animations + extra motion layer (30 Oct)</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr"/>
+          <t>New original design "The Earthen Atlas" (31 Oct): tension-as-terrain service animations, 17 pages; replaces Ember (30 Oct)</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="K2" s="7" t="inlineStr"/>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\earthenphoenix.com\2026-10-30_earthenphoenix.com_ember-site-preview</t>
+          <t>C:\Users\DaveDeibu\Desktop\VA-KIT\VA-KIT\OUTBOX\New\earthenphoenix.com\2026-10-31_earthen-phoenix-atlas-website</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Checked 30 Oct (capsule header stays at top, full-screen menu below it, page locks, links work)</t>
+          <t>Checked 31 Oct (header stays at top 0–64px while scrolling, menu panel starts exactly at the header bottom, page locks, Esc closes; checked at top and after scrolling, home + a session page)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>client: yoga price ($140 or $120), whether to show the street address and hours, more session photos, OK to reuse the 3 testimonials; developer: move the GHL booking calendar before launch</t>
+          <t>client: yoga price ($140 or $120), whether to show the street address and hours, OK to reuse the 3 testimonials; developer: move the GHL booking calendar before launch, optional real form inbox</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr"/>
@@ -6592,7 +6596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6869,17 +6873,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix "Ember" original design (newest; see Website redesigns above)</t>
+          <t>Earthen Phoenix "The Earthen Atlas" (newest; see Website redesigns above)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x</t>
+          <t>https://claude.ai/artifact/9Wp2ERpwNbSbJ5LZ7hxGiP</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>30 Oct 2026</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6889,12 +6893,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix full site extending the earlier home design (superseded)</t>
+          <t>Earthen Phoenix "Ember" original design (previous)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
+          <t>https://claude.ai/artifact/AMnmJyUqsrVg2kgWi25H3x</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -6909,17 +6913,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
+          <t>Earthen Phoenix full site extending the earlier home design (superseded)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
+          <t>https://claude.ai/artifact/QEntpxndXnFWCdw8vEkJ8o</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
+          <t>30 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6929,17 +6933,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix (older)</t>
+          <t>Earthen Phoenix (Massage, Yoga &amp; Reiki)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
+          <t>https://claude.ai/artifact/Jsn9NFxJmciVtundmDbW7H</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>15 Oct 2026</t>
+          <t>15 Oct 2026; 30 Oct 2026 home redesigned; later on 30 Oct 2026 animation layer rebuilt from her practice: full-width photo banner with "Release" (knotted lines loosen under cursor/finger, then breathe), massage pressure ripple on linen + drifting modality tags, yoga line flowing Vinyasa then holding Yin, tappable singing bowl with Reiki light (optional chime, off by default), sprig/constellation/tarot card, bowl-ring breathing circle, root timeline, breath-paced reviews, oil shimmer on products; earth/sand/clay/sage palette, one ember accent; sand garden removed; 30 Oct 2026 new page astrology-tarot.html (original design, client example used only as a prompt): star-trail hero over her candle photo, birth-chart wheel that turns to your sun sign, tarot cards with her four steps around a candle that reacts to air, oracle card, teas/rollies/tinctures animations, Oregon to SLC herb journey, $2/min cost meter; facts from her booking page. FLAG: booking page says yoga $140/60 min, home page says $120</t>
         </is>
       </c>
     </row>
@@ -6949,17 +6953,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Earthen Phoenix redesign (older)</t>
+          <t>Earthen Phoenix (older)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
+          <t>https://claude.ai/artifact/M8XVeqahZEGWSeeqTRxui1</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>14 Oct 2026</t>
+          <t>15 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6969,12 +6973,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning redesign preview</t>
+          <t>Earthen Phoenix redesign (older)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
+          <t>https://claude.ai/artifact/NA6jMpgeLEAc6mMBPQgKpc</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -6989,12 +6993,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning site preview (older)</t>
+          <t>Alpine Cleaning redesign preview</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
+          <t>https://claude.ai/artifact/TwW8FzDFCAz6kAQHYPbBLV</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -7009,12 +7013,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Alpine Cleaning preview (older)</t>
+          <t>Alpine Cleaning site preview (older)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
+          <t>https://claude.ai/artifact/RDm9uD6K7cwSuanyfzVqnT</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -7029,12 +7033,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+          <t>Alpine Cleaning preview (older)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+          <t>https://claude.ai/artifact/U6hwEex7gLgva8FFJCJiw6</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -7049,22 +7053,42 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>Utah Restoration Companies (Water, Fire &amp; Mold)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/ET4zFRQiGsMaT6RPg1bHwd</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>14 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>The 5-Layer Page Infographic</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>https://claude.ai/artifact/JfTPtc3pR4ATt1989Qziph</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -7088,6 +7112,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
